--- a/Data/National Accounts/PSA-19EDUC_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-19EDUC_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4285DF-D54E-42E0-BD8A-F43E68598794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E25110-1399-41C7-9F6E-6478B46893A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="EDUC" sheetId="19" r:id="rId1"/>
@@ -682,10 +682,10 @@
     <t>Table 20.7 Gross Value Added in Education, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -734,10 +734,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1227,7 +1229,7 @@
     </row>
     <row r="3" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1240,7 +1242,7 @@
     </row>
     <row r="6" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -2231,28 +2233,28 @@
         <v>176829.23358122614</v>
       </c>
       <c r="CT12" s="26">
-        <v>168359.77340023682</v>
+        <v>169760.29356079764</v>
       </c>
       <c r="CU12" s="26">
-        <v>194147.2095803858</v>
+        <v>195001.04190617503</v>
       </c>
       <c r="CV12" s="26">
-        <v>159361.80581482823</v>
+        <v>159054.08448567215</v>
       </c>
       <c r="CW12" s="26">
-        <v>194830.74221769127</v>
+        <v>194378.55410256406</v>
       </c>
       <c r="CX12" s="26">
-        <v>187688.09327552898</v>
+        <v>189320.6003829304</v>
       </c>
       <c r="CY12" s="26">
-        <v>229891.51526216336</v>
+        <v>230989.64446320556</v>
       </c>
       <c r="CZ12" s="26">
-        <v>176659.2150237172</v>
+        <v>176432.04313457015</v>
       </c>
       <c r="DA12" s="26">
-        <v>219043.02657996846</v>
+        <v>210751.68614065848</v>
       </c>
       <c r="DB12" s="20"/>
       <c r="DC12" s="20"/>
@@ -2622,28 +2624,28 @@
         <v>78316.02459144521</v>
       </c>
       <c r="CT13" s="26">
-        <v>79636.973774950107</v>
+        <v>79657.787462444496</v>
       </c>
       <c r="CU13" s="26">
         <v>84823.505099704911</v>
       </c>
       <c r="CV13" s="26">
-        <v>83919.915399997291</v>
+        <v>84674.267116951407</v>
       </c>
       <c r="CW13" s="26">
-        <v>88000.492502709472</v>
+        <v>88214.427706654766</v>
       </c>
       <c r="CX13" s="26">
-        <v>88497.473039610355</v>
+        <v>88445.590798640609</v>
       </c>
       <c r="CY13" s="26">
-        <v>95741.292018958804</v>
+        <v>95864.299468568104</v>
       </c>
       <c r="CZ13" s="26">
-        <v>92167.361236655968</v>
+        <v>92890.56782039786</v>
       </c>
       <c r="DA13" s="26">
-        <v>97583.350027503126</v>
+        <v>98227.690031028469</v>
       </c>
       <c r="DB13" s="20"/>
       <c r="DC13" s="20"/>
@@ -3193,28 +3195,28 @@
         <v>255145.25817267137</v>
       </c>
       <c r="CT15" s="16">
-        <v>247996.74717518693</v>
+        <v>249418.08102324215</v>
       </c>
       <c r="CU15" s="16">
-        <v>278970.71468009072</v>
+        <v>279824.54700587993</v>
       </c>
       <c r="CV15" s="16">
-        <v>243281.72121482552</v>
+        <v>243728.35160262356</v>
       </c>
       <c r="CW15" s="16">
-        <v>282831.23472040077</v>
+        <v>282592.98180921882</v>
       </c>
       <c r="CX15" s="16">
-        <v>276185.56631513935</v>
+        <v>277766.19118157099</v>
       </c>
       <c r="CY15" s="16">
-        <v>325632.80728112219</v>
+        <v>326853.94393177365</v>
       </c>
       <c r="CZ15" s="16">
-        <v>268826.57626037317</v>
+        <v>269322.61095496803</v>
       </c>
       <c r="DA15" s="16">
-        <v>316626.37660747161</v>
+        <v>308979.37617168692</v>
       </c>
       <c r="DB15" s="20"/>
       <c r="DC15" s="20"/>
@@ -4087,7 +4089,7 @@
     </row>
     <row r="22" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4412,7 +4414,7 @@
     </row>
     <row r="25" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -5611,28 +5613,28 @@
         <v>132175.92810071129</v>
       </c>
       <c r="CT31" s="26">
-        <v>147747.86051204643</v>
+        <v>148870.71885601623</v>
       </c>
       <c r="CU31" s="26">
-        <v>167964.02713479899</v>
+        <v>169077.69954132158</v>
       </c>
       <c r="CV31" s="26">
-        <v>132077.65502247788</v>
+        <v>132421.77442923764</v>
       </c>
       <c r="CW31" s="26">
-        <v>141178.44662462836</v>
+        <v>141459.54722081285</v>
       </c>
       <c r="CX31" s="26">
-        <v>158079.12450786741</v>
+        <v>159280.49868239649</v>
       </c>
       <c r="CY31" s="26">
-        <v>191887.6656960549</v>
+        <v>193159.96192568881</v>
       </c>
       <c r="CZ31" s="26">
-        <v>141071.2394518693</v>
+        <v>141438.79103523726</v>
       </c>
       <c r="DA31" s="26">
-        <v>152665.075210457</v>
+        <v>147415.22929205815</v>
       </c>
       <c r="DB31" s="20"/>
       <c r="DC31" s="20"/>
@@ -6002,28 +6004,28 @@
         <v>65512.500837123953</v>
       </c>
       <c r="CT32" s="26">
-        <v>75301.910777375509</v>
+        <v>75321.586761613085</v>
       </c>
       <c r="CU32" s="26">
         <v>78635.340298839496</v>
       </c>
       <c r="CV32" s="26">
-        <v>69122.062725288561</v>
+        <v>69743.39732086935</v>
       </c>
       <c r="CW32" s="26">
-        <v>70023.719786426052</v>
+        <v>70193.952228853057</v>
       </c>
       <c r="CX32" s="26">
-        <v>79790.166241331404</v>
+        <v>79743.397065133729</v>
       </c>
       <c r="CY32" s="26">
-        <v>84199.997692719757</v>
+        <v>84308.17700339001</v>
       </c>
       <c r="CZ32" s="26">
-        <v>73000.113697345587</v>
+        <v>73572.921274035005</v>
       </c>
       <c r="DA32" s="26">
-        <v>75046.450850465975</v>
+        <v>75541.980368482356</v>
       </c>
       <c r="DB32" s="20"/>
       <c r="DC32" s="20"/>
@@ -6573,28 +6575,28 @@
         <v>197688.42893783524</v>
       </c>
       <c r="CT34" s="16">
-        <v>223049.77128942194</v>
+        <v>224192.30561762932</v>
       </c>
       <c r="CU34" s="16">
-        <v>246599.36743363849</v>
+        <v>247713.03984016107</v>
       </c>
       <c r="CV34" s="16">
-        <v>201199.71774776644</v>
+        <v>202165.17175010699</v>
       </c>
       <c r="CW34" s="16">
-        <v>211202.16641105441</v>
+        <v>211653.49944966589</v>
       </c>
       <c r="CX34" s="16">
-        <v>237869.29074919882</v>
+        <v>239023.89574753022</v>
       </c>
       <c r="CY34" s="16">
-        <v>276087.66338877467</v>
+        <v>277468.13892907882</v>
       </c>
       <c r="CZ34" s="16">
-        <v>214071.35314921488</v>
+        <v>215011.71230927226</v>
       </c>
       <c r="DA34" s="16">
-        <v>227711.52606092297</v>
+        <v>222957.20966054051</v>
       </c>
       <c r="DB34" s="20"/>
       <c r="DC34" s="20"/>
@@ -7467,7 +7469,7 @@
     </row>
     <row r="41" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -7792,7 +7794,7 @@
     </row>
     <row r="44" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -8925,28 +8927,28 @@
         <v>10.002792501671891</v>
       </c>
       <c r="CP50" s="13">
-        <v>6.5433918516505827</v>
+        <v>7.4296853245459147</v>
       </c>
       <c r="CQ50" s="13">
-        <v>2.1540991962020399</v>
+        <v>2.6033586642835616</v>
       </c>
       <c r="CR50" s="13">
-        <v>7.3579613047331804</v>
+        <v>7.1506573376423148</v>
       </c>
       <c r="CS50" s="13">
-        <v>10.180165503118673</v>
+        <v>9.9244452774697152</v>
       </c>
       <c r="CT50" s="13">
-        <v>11.480367005094209</v>
+        <v>11.522309729705711</v>
       </c>
       <c r="CU50" s="13">
-        <v>18.410929396838839</v>
+        <v>18.455595008741781</v>
       </c>
       <c r="CV50" s="13">
-        <v>10.854174951423332</v>
+        <v>10.925817281016407</v>
       </c>
       <c r="CW50" s="13">
-        <v>12.427342875501623</v>
+        <v>8.423322271167379</v>
       </c>
       <c r="CX50" s="15"/>
       <c r="CY50" s="15"/>
@@ -9304,28 +9306,28 @@
         <v>12.903705107622216</v>
       </c>
       <c r="CP51" s="13">
-        <v>14.80471860668915</v>
+        <v>14.834723633534026</v>
       </c>
       <c r="CQ51" s="13">
         <v>14.909409048235034</v>
       </c>
       <c r="CR51" s="13">
-        <v>12.33211127162825</v>
+        <v>13.341858726722052</v>
       </c>
       <c r="CS51" s="13">
-        <v>12.365882923431926</v>
+        <v>12.639052054604434</v>
       </c>
       <c r="CT51" s="13">
-        <v>11.126112463413733</v>
+        <v>11.031945044091529</v>
       </c>
       <c r="CU51" s="13">
-        <v>12.871181055794253</v>
+        <v>13.016196814651096</v>
       </c>
       <c r="CV51" s="13">
-        <v>9.8277575678525295</v>
+        <v>9.7034211020665424</v>
       </c>
       <c r="CW51" s="13">
-        <v>10.889549878938027</v>
+        <v>11.3510483315399</v>
       </c>
       <c r="CX51" s="15"/>
       <c r="CY51" s="15"/>
@@ -9860,28 +9862,28 @@
         <v>10.877236450087054</v>
       </c>
       <c r="CP53" s="13">
-        <v>9.0636133230177478</v>
+        <v>9.6886852522786171</v>
       </c>
       <c r="CQ53" s="13">
-        <v>5.7223878994491599</v>
+        <v>6.0459673563527048</v>
       </c>
       <c r="CR53" s="13">
-        <v>9.0232503944305051</v>
+        <v>9.2234014635676118</v>
       </c>
       <c r="CS53" s="13">
-        <v>10.851064505769784</v>
+        <v>10.757685184167528</v>
       </c>
       <c r="CT53" s="13">
-        <v>11.366608417665901</v>
+        <v>11.365699728756724</v>
       </c>
       <c r="CU53" s="13">
-        <v>16.72652007739994</v>
+        <v>16.80674459374913</v>
       </c>
       <c r="CV53" s="13">
-        <v>10.500112757337291</v>
+        <v>10.501141612804048</v>
       </c>
       <c r="CW53" s="13">
-        <v>11.948871884846739</v>
+        <v>9.3372433361709568</v>
       </c>
       <c r="CX53" s="15"/>
       <c r="CY53" s="15"/>
@@ -10746,7 +10748,7 @@
     </row>
     <row r="60" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -11071,7 +11073,7 @@
     </row>
     <row r="63" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -12248,28 +12250,28 @@
         <v>5.8093533399945301</v>
       </c>
       <c r="CP69" s="13">
-        <v>3.0767224646506719</v>
+        <v>3.8600878378437073</v>
       </c>
       <c r="CQ69" s="13">
-        <v>-1.5032634400494231</v>
+        <v>-0.85018849590494483</v>
       </c>
       <c r="CR69" s="13">
-        <v>3.3007769759348093</v>
+        <v>3.5699201711613853</v>
       </c>
       <c r="CS69" s="13">
-        <v>6.8110121512122959</v>
+        <v>7.023683702094317</v>
       </c>
       <c r="CT69" s="13">
         <v>6.9924965140044151</v>
       </c>
       <c r="CU69" s="13">
-        <v>14.243310885881584</v>
+        <v>14.243310885881598</v>
       </c>
       <c r="CV69" s="13">
-        <v>6.8093156468146105</v>
+        <v>6.8093156468145963</v>
       </c>
       <c r="CW69" s="13">
-        <v>8.1362480325129383</v>
+        <v>4.2101662194271796</v>
       </c>
       <c r="CX69" s="15"/>
       <c r="CY69" s="15"/>
@@ -12627,28 +12629,28 @@
         <v>8.4250111462042838</v>
       </c>
       <c r="CP70" s="13">
-        <v>9.9031016188410774</v>
+        <v>9.9318187081258884</v>
       </c>
       <c r="CQ70" s="13">
         <v>10.060028112688443</v>
       </c>
       <c r="CR70" s="13">
-        <v>5.7845318039115199</v>
+        <v>6.735423410666769</v>
       </c>
       <c r="CS70" s="13">
-        <v>6.8860429561646868</v>
+        <v>7.1458902223379397</v>
       </c>
       <c r="CT70" s="13">
-        <v>5.9603473771403941</v>
+        <v>5.8705750816367299</v>
       </c>
       <c r="CU70" s="13">
-        <v>7.0765350194108407</v>
+        <v>7.214105875287018</v>
       </c>
       <c r="CV70" s="13">
-        <v>5.6104387212365907</v>
+        <v>5.4908766998359937</v>
       </c>
       <c r="CW70" s="13">
-        <v>7.1728995251314274</v>
+        <v>7.6189300784676561</v>
       </c>
       <c r="CX70" s="15"/>
       <c r="CY70" s="15"/>
@@ -13182,28 +13184,28 @@
         <v>6.6620692858968766</v>
       </c>
       <c r="CP72" s="13">
-        <v>5.284467810419784</v>
+        <v>5.8237695008230617</v>
       </c>
       <c r="CQ72" s="13">
-        <v>1.9110138631643281</v>
+        <v>2.371256260544726</v>
       </c>
       <c r="CR72" s="13">
-        <v>4.1408109169785519</v>
+        <v>4.6405291264883317</v>
       </c>
       <c r="CS72" s="13">
-        <v>6.8358768117220876</v>
+        <v>7.0641820499378127</v>
       </c>
       <c r="CT72" s="13">
-        <v>6.6440415401939816</v>
+        <v>6.6155660824492628</v>
       </c>
       <c r="CU72" s="13">
-        <v>11.95797712784956</v>
+        <v>12.011922791031694</v>
       </c>
       <c r="CV72" s="13">
-        <v>6.3974420767254401</v>
+        <v>6.3544776026232057</v>
       </c>
       <c r="CW72" s="13">
-        <v>7.816851470044611</v>
+        <v>5.3406677613486693</v>
       </c>
       <c r="CX72" s="15"/>
       <c r="CY72" s="15"/>
@@ -13936,7 +13938,7 @@
     </row>
     <row r="78" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -14192,7 +14194,7 @@
     </row>
     <row r="81" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -15283,28 +15285,28 @@
         <v>133.78323581468732</v>
       </c>
       <c r="CT87" s="13">
-        <v>113.95073527072145</v>
+        <v>114.03202380246799</v>
       </c>
       <c r="CU87" s="13">
-        <v>115.58856553526999</v>
+        <v>115.33220669265016</v>
       </c>
       <c r="CV87" s="13">
-        <v>120.65765839627221</v>
+        <v>120.1117302431754</v>
       </c>
       <c r="CW87" s="13">
-        <v>138.00317745081588</v>
+        <v>137.40928620331769</v>
       </c>
       <c r="CX87" s="13">
-        <v>118.73047365352025</v>
+        <v>118.85987421500576</v>
       </c>
       <c r="CY87" s="13">
-        <v>119.80525920113362</v>
+        <v>119.58463967396635</v>
       </c>
       <c r="CZ87" s="13">
-        <v>125.2269532118131</v>
+        <v>124.74091572984025</v>
       </c>
       <c r="DA87" s="13">
-        <v>143.4794606939445</v>
+        <v>142.96466325274881</v>
       </c>
       <c r="DB87" s="20"/>
       <c r="DC87" s="20"/>
@@ -15670,7 +15672,7 @@
         <v>119.54363455938457</v>
       </c>
       <c r="CT88" s="13">
-        <v>105.75690968903947</v>
+        <v>105.75691629353898</v>
       </c>
       <c r="CU88" s="13">
         <v>107.86944493067419</v>
@@ -15679,10 +15681,10 @@
         <v>121.40829149373009</v>
       </c>
       <c r="CW88" s="13">
-        <v>125.67240468103236</v>
+        <v>125.67240468103238</v>
       </c>
       <c r="CX88" s="13">
-        <v>110.91275680757833</v>
+        <v>110.91274519744752</v>
       </c>
       <c r="CY88" s="13">
         <v>113.70700076306173</v>
@@ -15691,7 +15693,7 @@
         <v>126.25646258412245</v>
       </c>
       <c r="DA88" s="13">
-        <v>130.03059961082386</v>
+        <v>130.03059961082388</v>
       </c>
       <c r="DB88" s="20"/>
       <c r="DC88" s="20"/>
@@ -16233,28 +16235,28 @@
         <v>129.06433600770021</v>
       </c>
       <c r="CT90" s="13">
-        <v>111.18448844020317</v>
+        <v>111.25184708552692</v>
       </c>
       <c r="CU90" s="13">
-        <v>113.12710068291784</v>
+        <v>112.96318804469846</v>
       </c>
       <c r="CV90" s="13">
-        <v>120.91553802268007</v>
+        <v>120.55902087026746</v>
       </c>
       <c r="CW90" s="13">
-        <v>133.91493066881594</v>
+        <v>133.51680106589654</v>
       </c>
       <c r="CX90" s="13">
-        <v>116.10812200484504</v>
+        <v>116.20854488747956</v>
       </c>
       <c r="CY90" s="13">
-        <v>117.94543924354208</v>
+        <v>117.79873004277364</v>
       </c>
       <c r="CZ90" s="13">
-        <v>125.57802447905866</v>
+        <v>125.25950705772489</v>
       </c>
       <c r="DA90" s="13">
-        <v>139.04714534421942</v>
+        <v>138.58236593565104</v>
       </c>
       <c r="DB90" s="20"/>
       <c r="DC90" s="20"/>
@@ -16948,7 +16950,7 @@
     </row>
     <row r="97" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -17273,7 +17275,7 @@
     </row>
     <row r="100" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -18472,28 +18474,28 @@
         <v>69.305318408682993</v>
       </c>
       <c r="CT106" s="13">
-        <v>67.887895836515185</v>
+        <v>68.062544970417932</v>
       </c>
       <c r="CU106" s="13">
-        <v>69.594118437494004</v>
+        <v>69.686896304375139</v>
       </c>
       <c r="CV106" s="13">
-        <v>65.505046996155812</v>
+        <v>65.258753624607067</v>
       </c>
       <c r="CW106" s="13">
-        <v>68.885864890522299</v>
+        <v>68.783928340368632</v>
       </c>
       <c r="CX106" s="13">
-        <v>67.957241857226165</v>
+        <v>68.158259137871383</v>
       </c>
       <c r="CY106" s="13">
-        <v>70.598388774659199</v>
+        <v>70.67060035580343</v>
       </c>
       <c r="CZ106" s="13">
-        <v>65.714936923726299</v>
+        <v>65.509554696865166</v>
       </c>
       <c r="DA106" s="13">
-        <v>69.180284007583083</v>
+        <v>68.208981697067244</v>
       </c>
       <c r="DB106" s="20"/>
       <c r="DC106" s="20"/>
@@ -18863,28 +18865,28 @@
         <v>30.694681591317007</v>
       </c>
       <c r="CT107" s="13">
-        <v>32.112104163484808</v>
+        <v>31.937455029582058</v>
       </c>
       <c r="CU107" s="13">
-        <v>30.405881562505993</v>
+        <v>30.313103695624861</v>
       </c>
       <c r="CV107" s="13">
-        <v>34.494953003844188</v>
+        <v>34.74124637539294</v>
       </c>
       <c r="CW107" s="13">
-        <v>31.114135109477694</v>
+        <v>31.216071659631361</v>
       </c>
       <c r="CX107" s="13">
-        <v>32.042758142773835</v>
+        <v>31.841740862128624</v>
       </c>
       <c r="CY107" s="13">
-        <v>29.401611225340801</v>
+        <v>29.329399644196581</v>
       </c>
       <c r="CZ107" s="13">
-        <v>34.285063076273701</v>
+        <v>34.490445303134834</v>
       </c>
       <c r="DA107" s="13">
-        <v>30.819715992416914</v>
+        <v>31.791018302932766</v>
       </c>
       <c r="DB107" s="20"/>
       <c r="DC107" s="20"/>
@@ -20328,7 +20330,7 @@
     </row>
     <row r="116" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -20653,7 +20655,7 @@
     </row>
     <row r="119" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -21852,28 +21854,28 @@
         <v>66.860730701782799</v>
       </c>
       <c r="CT125" s="13">
-        <v>66.239861918680802</v>
+        <v>66.403134775696699</v>
       </c>
       <c r="CU125" s="13">
-        <v>68.112107862563448</v>
+        <v>68.255469978657729</v>
       </c>
       <c r="CV125" s="13">
-        <v>65.645049854422126</v>
+        <v>65.501774258585939</v>
       </c>
       <c r="CW125" s="13">
-        <v>66.845169736497084</v>
+        <v>66.835439805451387</v>
       </c>
       <c r="CX125" s="13">
-        <v>66.456297914698283</v>
+        <v>66.637897514078276</v>
       </c>
       <c r="CY125" s="13">
-        <v>69.50244112350903</v>
+        <v>69.615186331379377</v>
       </c>
       <c r="CZ125" s="13">
-        <v>65.899167439530288</v>
+        <v>65.781900677016182</v>
       </c>
       <c r="DA125" s="13">
-        <v>67.043191818762963</v>
+        <v>66.118171068117761</v>
       </c>
       <c r="DB125" s="20"/>
       <c r="DC125" s="20"/>
@@ -22243,28 +22245,28 @@
         <v>33.139269298217194</v>
       </c>
       <c r="CT126" s="13">
-        <v>33.760138081319198</v>
+        <v>33.596865224303301</v>
       </c>
       <c r="CU126" s="13">
-        <v>31.887892137436559</v>
+        <v>31.744530021342282</v>
       </c>
       <c r="CV126" s="13">
-        <v>34.354950145577881</v>
+        <v>34.498225741414061</v>
       </c>
       <c r="CW126" s="13">
-        <v>33.154830263502916</v>
+        <v>33.164560194548606</v>
       </c>
       <c r="CX126" s="13">
-        <v>33.54370208530171</v>
+        <v>33.362102485921724</v>
       </c>
       <c r="CY126" s="13">
-        <v>30.49755887649097</v>
+        <v>30.384813668620623</v>
       </c>
       <c r="CZ126" s="13">
-        <v>34.100832560469719</v>
+        <v>34.218099322983818</v>
       </c>
       <c r="DA126" s="13">
-        <v>32.956808181237044</v>
+        <v>33.881828931882239</v>
       </c>
       <c r="DB126" s="20"/>
       <c r="DC126" s="20"/>

--- a/Data/National Accounts/PSA-19EDUC_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-19EDUC_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E25110-1399-41C7-9F6E-6478B46893A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C0EC8C-74C3-4DD5-B1B0-54A1116C6416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="EDUC" sheetId="19" r:id="rId1"/>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">EDUC!$A$1:$DA$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">EDUC!$A$1:$DB$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -682,10 +682,13 @@
     <t>Table 20.7 Gross Value Added in Education, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1213,8 +1216,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="4" customWidth="1"/>
-    <col min="2" max="105" width="13" style="21" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="21"/>
+    <col min="2" max="106" width="13" style="21" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1229,7 +1232,7 @@
     </row>
     <row r="3" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1242,7 +1245,7 @@
     </row>
     <row r="6" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1356,6 +1359,7 @@
       <c r="CY8" s="4"/>
       <c r="CZ8" s="4"/>
       <c r="DA8" s="4"/>
+      <c r="DB8" s="4"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
@@ -1515,6 +1519,9 @@
       <c r="CY9" s="25"/>
       <c r="CZ9" s="25"/>
       <c r="DA9" s="25"/>
+      <c r="DB9" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1831,6 +1838,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1939,6 +1949,7 @@
       <c r="CY11" s="4"/>
       <c r="CZ11" s="4"/>
       <c r="DA11" s="4"/>
+      <c r="DB11" s="4"/>
     </row>
     <row r="12" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2256,7 +2267,9 @@
       <c r="DA12" s="26">
         <v>210751.68614065848</v>
       </c>
-      <c r="DB12" s="20"/>
+      <c r="DB12" s="26">
+        <v>209966.11300975404</v>
+      </c>
       <c r="DC12" s="20"/>
       <c r="DD12" s="20"/>
       <c r="DE12" s="20"/>
@@ -2647,7 +2660,9 @@
       <c r="DA13" s="26">
         <v>98227.690031028469</v>
       </c>
-      <c r="DB13" s="20"/>
+      <c r="DB13" s="26">
+        <v>95797.542987904744</v>
+      </c>
       <c r="DC13" s="20"/>
       <c r="DD13" s="20"/>
       <c r="DE13" s="20"/>
@@ -2827,7 +2842,7 @@
       <c r="CY14" s="8"/>
       <c r="CZ14" s="8"/>
       <c r="DA14" s="8"/>
-      <c r="DB14" s="20"/>
+      <c r="DB14" s="8"/>
       <c r="DC14" s="20"/>
       <c r="DD14" s="20"/>
       <c r="DE14" s="20"/>
@@ -3218,7 +3233,9 @@
       <c r="DA15" s="16">
         <v>308979.37617168692</v>
       </c>
-      <c r="DB15" s="20"/>
+      <c r="DB15" s="16">
+        <v>305763.65599765879</v>
+      </c>
       <c r="DC15" s="20"/>
       <c r="DD15" s="20"/>
       <c r="DE15" s="20"/>
@@ -3399,6 +3416,7 @@
       <c r="CY16" s="10"/>
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
+      <c r="DB16" s="10"/>
     </row>
     <row r="17" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3508,6 +3526,7 @@
       <c r="CY17" s="4"/>
       <c r="CZ17" s="4"/>
       <c r="DA17" s="4"/>
+      <c r="DB17" s="4"/>
     </row>
     <row r="18" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="8"/>
@@ -3614,7 +3633,7 @@
       <c r="CY18" s="8"/>
       <c r="CZ18" s="8"/>
       <c r="DA18" s="8"/>
-      <c r="DB18" s="20"/>
+      <c r="DB18" s="8"/>
       <c r="DC18" s="20"/>
       <c r="DD18" s="20"/>
       <c r="DE18" s="20"/>
@@ -3794,7 +3813,7 @@
       <c r="CY19" s="8"/>
       <c r="CZ19" s="8"/>
       <c r="DA19" s="8"/>
-      <c r="DB19" s="20"/>
+      <c r="DB19" s="8"/>
       <c r="DC19" s="20"/>
       <c r="DD19" s="20"/>
       <c r="DE19" s="20"/>
@@ -3977,6 +3996,7 @@
       <c r="CY20" s="4"/>
       <c r="CZ20" s="4"/>
       <c r="DA20" s="4"/>
+      <c r="DB20" s="4"/>
     </row>
     <row r="21" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -4086,10 +4106,11 @@
       <c r="CY21" s="4"/>
       <c r="CZ21" s="4"/>
       <c r="DA21" s="4"/>
+      <c r="DB21" s="4"/>
     </row>
     <row r="22" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4195,6 +4216,7 @@
       <c r="CY22" s="4"/>
       <c r="CZ22" s="4"/>
       <c r="DA22" s="4"/>
+      <c r="DB22" s="4"/>
     </row>
     <row r="23" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
@@ -4302,6 +4324,7 @@
       <c r="CY23" s="4"/>
       <c r="CZ23" s="4"/>
       <c r="DA23" s="4"/>
+      <c r="DB23" s="4"/>
     </row>
     <row r="24" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
@@ -4411,10 +4434,11 @@
       <c r="CY24" s="4"/>
       <c r="CZ24" s="4"/>
       <c r="DA24" s="4"/>
+      <c r="DB24" s="4"/>
     </row>
     <row r="25" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -4520,6 +4544,7 @@
       <c r="CY25" s="4"/>
       <c r="CZ25" s="4"/>
       <c r="DA25" s="4"/>
+      <c r="DB25" s="4"/>
     </row>
     <row r="26" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -4629,6 +4654,7 @@
       <c r="CY26" s="4"/>
       <c r="CZ26" s="4"/>
       <c r="DA26" s="4"/>
+      <c r="DB26" s="4"/>
     </row>
     <row r="27" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
@@ -4736,6 +4762,7 @@
       <c r="CY27" s="4"/>
       <c r="CZ27" s="4"/>
       <c r="DA27" s="4"/>
+      <c r="DB27" s="4"/>
     </row>
     <row r="28" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
@@ -4895,6 +4922,9 @@
       <c r="CY28" s="25"/>
       <c r="CZ28" s="25"/>
       <c r="DA28" s="25"/>
+      <c r="DB28" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="29" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -5211,6 +5241,9 @@
       </c>
       <c r="DA29" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB29" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5319,6 +5352,7 @@
       <c r="CY30" s="4"/>
       <c r="CZ30" s="4"/>
       <c r="DA30" s="4"/>
+      <c r="DB30" s="4"/>
     </row>
     <row r="31" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
@@ -5636,7 +5670,9 @@
       <c r="DA31" s="26">
         <v>147415.22929205815</v>
       </c>
-      <c r="DB31" s="20"/>
+      <c r="DB31" s="26">
+        <v>169848.30677848676</v>
+      </c>
       <c r="DC31" s="20"/>
       <c r="DD31" s="20"/>
       <c r="DE31" s="20"/>
@@ -6027,7 +6063,9 @@
       <c r="DA32" s="26">
         <v>75541.980368482356</v>
       </c>
-      <c r="DB32" s="20"/>
+      <c r="DB32" s="26">
+        <v>83766.168252039715</v>
+      </c>
       <c r="DC32" s="20"/>
       <c r="DD32" s="20"/>
       <c r="DE32" s="20"/>
@@ -6207,7 +6245,7 @@
       <c r="CY33" s="8"/>
       <c r="CZ33" s="8"/>
       <c r="DA33" s="8"/>
-      <c r="DB33" s="20"/>
+      <c r="DB33" s="8"/>
       <c r="DC33" s="20"/>
       <c r="DD33" s="20"/>
       <c r="DE33" s="20"/>
@@ -6598,7 +6636,9 @@
       <c r="DA34" s="16">
         <v>222957.20966054051</v>
       </c>
-      <c r="DB34" s="20"/>
+      <c r="DB34" s="16">
+        <v>253614.47503052646</v>
+      </c>
       <c r="DC34" s="20"/>
       <c r="DD34" s="20"/>
       <c r="DE34" s="20"/>
@@ -6779,6 +6819,7 @@
       <c r="CY35" s="10"/>
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
+      <c r="DB35" s="10"/>
     </row>
     <row r="36" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -6888,6 +6929,7 @@
       <c r="CY36" s="4"/>
       <c r="CZ36" s="4"/>
       <c r="DA36" s="4"/>
+      <c r="DB36" s="4"/>
     </row>
     <row r="37" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8"/>
@@ -6994,7 +7036,7 @@
       <c r="CY37" s="8"/>
       <c r="CZ37" s="8"/>
       <c r="DA37" s="8"/>
-      <c r="DB37" s="20"/>
+      <c r="DB37" s="8"/>
       <c r="DC37" s="20"/>
       <c r="DD37" s="20"/>
       <c r="DE37" s="20"/>
@@ -7174,7 +7216,7 @@
       <c r="CY38" s="7"/>
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
-      <c r="DB38" s="20"/>
+      <c r="DB38" s="7"/>
       <c r="DC38" s="20"/>
       <c r="DD38" s="20"/>
       <c r="DE38" s="20"/>
@@ -7357,6 +7399,7 @@
       <c r="CY39" s="27"/>
       <c r="CZ39" s="27"/>
       <c r="DA39" s="27"/>
+      <c r="DB39" s="27"/>
     </row>
     <row r="40" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
@@ -7466,10 +7509,11 @@
       <c r="CY40" s="27"/>
       <c r="CZ40" s="27"/>
       <c r="DA40" s="27"/>
+      <c r="DB40" s="27"/>
     </row>
     <row r="41" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -7575,6 +7619,7 @@
       <c r="CY41" s="27"/>
       <c r="CZ41" s="27"/>
       <c r="DA41" s="27"/>
+      <c r="DB41" s="27"/>
     </row>
     <row r="42" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
@@ -7682,6 +7727,7 @@
       <c r="CY42" s="27"/>
       <c r="CZ42" s="27"/>
       <c r="DA42" s="27"/>
+      <c r="DB42" s="27"/>
     </row>
     <row r="43" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
@@ -7791,10 +7837,11 @@
       <c r="CY43" s="27"/>
       <c r="CZ43" s="27"/>
       <c r="DA43" s="27"/>
+      <c r="DB43" s="27"/>
     </row>
     <row r="44" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -7879,6 +7926,7 @@
       <c r="CY44" s="18"/>
       <c r="CZ44" s="18"/>
       <c r="DA44" s="18"/>
+      <c r="DB44" s="18"/>
     </row>
     <row r="45" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
@@ -7965,6 +8013,7 @@
       <c r="CY45" s="18"/>
       <c r="CZ45" s="18"/>
       <c r="DA45" s="18"/>
+      <c r="DB45" s="18"/>
     </row>
     <row r="46" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
@@ -8068,10 +8117,11 @@
       <c r="CU46" s="4"/>
       <c r="CV46" s="4"/>
       <c r="CW46" s="4"/>
-      <c r="CX46" s="27"/>
+      <c r="CX46" s="4"/>
       <c r="CY46" s="27"/>
       <c r="CZ46" s="27"/>
       <c r="DA46" s="27"/>
+      <c r="DB46" s="27"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="14"/>
@@ -8225,10 +8275,13 @@
       <c r="CU47" s="25"/>
       <c r="CV47" s="25"/>
       <c r="CW47" s="25"/>
-      <c r="CX47" s="28"/>
+      <c r="CX47" s="25" t="s">
+        <v>53</v>
+      </c>
       <c r="CY47" s="28"/>
       <c r="CZ47" s="28"/>
       <c r="DA47" s="28"/>
+      <c r="DB47" s="28"/>
     </row>
     <row r="48" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -8534,10 +8587,13 @@
       <c r="CW48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX48" s="29"/>
+      <c r="CX48" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY48" s="29"/>
       <c r="CZ48" s="29"/>
       <c r="DA48" s="29"/>
+      <c r="DB48" s="29"/>
     </row>
     <row r="49" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
@@ -8641,10 +8697,11 @@
       <c r="CU49" s="4"/>
       <c r="CV49" s="4"/>
       <c r="CW49" s="4"/>
-      <c r="CX49" s="27"/>
+      <c r="CX49" s="4"/>
       <c r="CY49" s="27"/>
       <c r="CZ49" s="27"/>
       <c r="DA49" s="27"/>
+      <c r="DB49" s="27"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -8950,11 +9007,13 @@
       <c r="CW50" s="13">
         <v>8.423322271167379</v>
       </c>
-      <c r="CX50" s="15"/>
+      <c r="CX50" s="13">
+        <v>10.905053430564294</v>
+      </c>
       <c r="CY50" s="15"/>
       <c r="CZ50" s="15"/>
       <c r="DA50" s="15"/>
-      <c r="DB50" s="20"/>
+      <c r="DB50" s="15"/>
       <c r="DC50" s="20"/>
       <c r="DD50" s="20"/>
       <c r="DE50" s="20"/>
@@ -9329,11 +9388,13 @@
       <c r="CW51" s="13">
         <v>11.3510483315399</v>
       </c>
-      <c r="CX51" s="15"/>
+      <c r="CX51" s="13">
+        <v>8.3124010172558371</v>
+      </c>
       <c r="CY51" s="15"/>
       <c r="CZ51" s="15"/>
       <c r="DA51" s="15"/>
-      <c r="DB51" s="20"/>
+      <c r="DB51" s="15"/>
       <c r="DC51" s="20"/>
       <c r="DD51" s="20"/>
       <c r="DE51" s="20"/>
@@ -9506,11 +9567,11 @@
       <c r="CU52" s="8"/>
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
-      <c r="CX52" s="7"/>
+      <c r="CX52" s="8"/>
       <c r="CY52" s="7"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
-      <c r="DB52" s="20"/>
+      <c r="DB52" s="7"/>
       <c r="DC52" s="20"/>
       <c r="DD52" s="20"/>
       <c r="DE52" s="20"/>
@@ -9885,11 +9946,13 @@
       <c r="CW53" s="13">
         <v>9.3372433361709568</v>
       </c>
-      <c r="CX53" s="15"/>
+      <c r="CX53" s="13">
+        <v>10.079507767662889</v>
+      </c>
       <c r="CY53" s="15"/>
       <c r="CZ53" s="15"/>
       <c r="DA53" s="15"/>
-      <c r="DB53" s="20"/>
+      <c r="DB53" s="15"/>
       <c r="DC53" s="20"/>
       <c r="DD53" s="20"/>
       <c r="DE53" s="20"/>
@@ -10062,10 +10125,11 @@
       <c r="CU54" s="10"/>
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
-      <c r="CX54" s="30"/>
+      <c r="CX54" s="10"/>
       <c r="CY54" s="30"/>
       <c r="CZ54" s="30"/>
       <c r="DA54" s="30"/>
+      <c r="DB54" s="30"/>
     </row>
     <row r="55" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
@@ -10171,10 +10235,11 @@
       <c r="CU55" s="4"/>
       <c r="CV55" s="4"/>
       <c r="CW55" s="4"/>
-      <c r="CX55" s="27"/>
+      <c r="CX55" s="4"/>
       <c r="CY55" s="27"/>
       <c r="CZ55" s="27"/>
       <c r="DA55" s="27"/>
+      <c r="DB55" s="27"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="8"/>
@@ -10277,11 +10342,11 @@
       <c r="CU56" s="8"/>
       <c r="CV56" s="8"/>
       <c r="CW56" s="8"/>
-      <c r="CX56" s="7"/>
+      <c r="CX56" s="8"/>
       <c r="CY56" s="7"/>
       <c r="CZ56" s="7"/>
       <c r="DA56" s="7"/>
-      <c r="DB56" s="20"/>
+      <c r="DB56" s="7"/>
       <c r="DC56" s="20"/>
       <c r="DD56" s="20"/>
       <c r="DE56" s="20"/>
@@ -10453,11 +10518,11 @@
       <c r="CU57" s="8"/>
       <c r="CV57" s="8"/>
       <c r="CW57" s="8"/>
-      <c r="CX57" s="7"/>
+      <c r="CX57" s="8"/>
       <c r="CY57" s="7"/>
       <c r="CZ57" s="7"/>
       <c r="DA57" s="7"/>
-      <c r="DB57" s="20"/>
+      <c r="DB57" s="7"/>
       <c r="DC57" s="20"/>
       <c r="DD57" s="20"/>
       <c r="DE57" s="20"/>
@@ -10632,10 +10697,11 @@
       <c r="CU58" s="4"/>
       <c r="CV58" s="4"/>
       <c r="CW58" s="4"/>
-      <c r="CX58" s="27"/>
+      <c r="CX58" s="4"/>
       <c r="CY58" s="27"/>
       <c r="CZ58" s="27"/>
       <c r="DA58" s="27"/>
+      <c r="DB58" s="27"/>
     </row>
     <row r="59" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
@@ -10741,14 +10807,15 @@
       <c r="CU59" s="4"/>
       <c r="CV59" s="4"/>
       <c r="CW59" s="4"/>
-      <c r="CX59" s="27"/>
+      <c r="CX59" s="4"/>
       <c r="CY59" s="27"/>
       <c r="CZ59" s="27"/>
       <c r="DA59" s="27"/>
+      <c r="DB59" s="27"/>
     </row>
     <row r="60" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -10850,10 +10917,11 @@
       <c r="CU60" s="4"/>
       <c r="CV60" s="4"/>
       <c r="CW60" s="4"/>
-      <c r="CX60" s="27"/>
+      <c r="CX60" s="4"/>
       <c r="CY60" s="27"/>
       <c r="CZ60" s="27"/>
       <c r="DA60" s="27"/>
+      <c r="DB60" s="27"/>
     </row>
     <row r="61" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
@@ -10957,10 +11025,11 @@
       <c r="CU61" s="4"/>
       <c r="CV61" s="4"/>
       <c r="CW61" s="4"/>
-      <c r="CX61" s="27"/>
+      <c r="CX61" s="4"/>
       <c r="CY61" s="27"/>
       <c r="CZ61" s="27"/>
       <c r="DA61" s="27"/>
+      <c r="DB61" s="27"/>
     </row>
     <row r="62" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
@@ -11066,14 +11135,15 @@
       <c r="CU62" s="4"/>
       <c r="CV62" s="4"/>
       <c r="CW62" s="4"/>
-      <c r="CX62" s="27"/>
+      <c r="CX62" s="4"/>
       <c r="CY62" s="27"/>
       <c r="CZ62" s="27"/>
       <c r="DA62" s="27"/>
+      <c r="DB62" s="27"/>
     </row>
     <row r="63" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -11175,10 +11245,11 @@
       <c r="CU63" s="4"/>
       <c r="CV63" s="4"/>
       <c r="CW63" s="4"/>
-      <c r="CX63" s="27"/>
+      <c r="CX63" s="4"/>
       <c r="CY63" s="27"/>
       <c r="CZ63" s="27"/>
       <c r="DA63" s="27"/>
+      <c r="DB63" s="27"/>
     </row>
     <row r="64" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
@@ -11284,10 +11355,11 @@
       <c r="CU64" s="4"/>
       <c r="CV64" s="4"/>
       <c r="CW64" s="4"/>
-      <c r="CX64" s="27"/>
+      <c r="CX64" s="4"/>
       <c r="CY64" s="27"/>
       <c r="CZ64" s="27"/>
       <c r="DA64" s="27"/>
+      <c r="DB64" s="27"/>
     </row>
     <row r="65" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
@@ -11391,10 +11463,11 @@
       <c r="CU65" s="4"/>
       <c r="CV65" s="4"/>
       <c r="CW65" s="4"/>
-      <c r="CX65" s="27"/>
+      <c r="CX65" s="4"/>
       <c r="CY65" s="27"/>
       <c r="CZ65" s="27"/>
       <c r="DA65" s="27"/>
+      <c r="DB65" s="27"/>
     </row>
     <row r="66" spans="1:175" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="14"/>
@@ -11548,10 +11621,13 @@
       <c r="CU66" s="25"/>
       <c r="CV66" s="25"/>
       <c r="CW66" s="25"/>
-      <c r="CX66" s="28"/>
+      <c r="CX66" s="25" t="s">
+        <v>53</v>
+      </c>
       <c r="CY66" s="28"/>
       <c r="CZ66" s="28"/>
       <c r="DA66" s="28"/>
+      <c r="DB66" s="28"/>
     </row>
     <row r="67" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -11857,10 +11933,13 @@
       <c r="CW67" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX67" s="29"/>
+      <c r="CX67" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY67" s="29"/>
       <c r="CZ67" s="29"/>
       <c r="DA67" s="29"/>
+      <c r="DB67" s="29"/>
     </row>
     <row r="68" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
@@ -11964,10 +12043,11 @@
       <c r="CU68" s="4"/>
       <c r="CV68" s="4"/>
       <c r="CW68" s="4"/>
-      <c r="CX68" s="27"/>
+      <c r="CX68" s="4"/>
       <c r="CY68" s="27"/>
       <c r="CZ68" s="27"/>
       <c r="DA68" s="27"/>
+      <c r="DB68" s="27"/>
     </row>
     <row r="69" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
@@ -12273,11 +12353,13 @@
       <c r="CW69" s="13">
         <v>4.2101662194271796</v>
       </c>
-      <c r="CX69" s="15"/>
+      <c r="CX69" s="13">
+        <v>6.6347156014135606</v>
+      </c>
       <c r="CY69" s="15"/>
       <c r="CZ69" s="15"/>
       <c r="DA69" s="15"/>
-      <c r="DB69" s="20"/>
+      <c r="DB69" s="15"/>
       <c r="DC69" s="20"/>
       <c r="DD69" s="20"/>
       <c r="DE69" s="20"/>
@@ -12652,11 +12734,13 @@
       <c r="CW70" s="13">
         <v>7.6189300784676561</v>
       </c>
-      <c r="CX70" s="15"/>
+      <c r="CX70" s="13">
+        <v>5.0446448671107191</v>
+      </c>
       <c r="CY70" s="15"/>
       <c r="CZ70" s="15"/>
       <c r="DA70" s="15"/>
-      <c r="DB70" s="20"/>
+      <c r="DB70" s="15"/>
       <c r="DC70" s="20"/>
       <c r="DD70" s="20"/>
       <c r="DE70" s="20"/>
@@ -12828,11 +12912,11 @@
       <c r="CU71" s="8"/>
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
-      <c r="CX71" s="7"/>
+      <c r="CX71" s="8"/>
       <c r="CY71" s="7"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
-      <c r="DB71" s="20"/>
+      <c r="DB71" s="7"/>
       <c r="DC71" s="20"/>
       <c r="DD71" s="20"/>
       <c r="DE71" s="20"/>
@@ -13207,11 +13291,13 @@
       <c r="CW72" s="13">
         <v>5.3406677613486693</v>
       </c>
-      <c r="CX72" s="15"/>
+      <c r="CX72" s="13">
+        <v>6.1042345734367842</v>
+      </c>
       <c r="CY72" s="15"/>
       <c r="CZ72" s="15"/>
       <c r="DA72" s="15"/>
-      <c r="DB72" s="20"/>
+      <c r="DB72" s="15"/>
       <c r="DC72" s="20"/>
       <c r="DD72" s="20"/>
       <c r="DE72" s="20"/>
@@ -13384,10 +13470,11 @@
       <c r="CU73" s="10"/>
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
-      <c r="CX73" s="30"/>
+      <c r="CX73" s="10"/>
       <c r="CY73" s="30"/>
       <c r="CZ73" s="30"/>
       <c r="DA73" s="30"/>
+      <c r="DB73" s="30"/>
     </row>
     <row r="74" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
@@ -13493,10 +13580,11 @@
       <c r="CU74" s="4"/>
       <c r="CV74" s="4"/>
       <c r="CW74" s="4"/>
-      <c r="CX74" s="27"/>
+      <c r="CX74" s="4"/>
       <c r="CY74" s="27"/>
       <c r="CZ74" s="27"/>
       <c r="DA74" s="27"/>
+      <c r="DB74" s="27"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="8"/>
@@ -13599,11 +13687,11 @@
       <c r="CU75" s="8"/>
       <c r="CV75" s="20"/>
       <c r="CW75" s="20"/>
-      <c r="CX75" s="7"/>
+      <c r="CX75" s="8"/>
       <c r="CY75" s="7"/>
       <c r="CZ75" s="19"/>
       <c r="DA75" s="19"/>
-      <c r="DB75" s="20"/>
+      <c r="DB75" s="7"/>
       <c r="DC75" s="20"/>
       <c r="DD75" s="20"/>
       <c r="DE75" s="20"/>
@@ -13779,7 +13867,7 @@
       <c r="CY76" s="19"/>
       <c r="CZ76" s="19"/>
       <c r="DA76" s="19"/>
-      <c r="DB76" s="20"/>
+      <c r="DB76" s="19"/>
       <c r="DC76" s="20"/>
       <c r="DD76" s="20"/>
       <c r="DE76" s="20"/>
@@ -13935,10 +14023,11 @@
       <c r="CY77" s="18"/>
       <c r="CZ77" s="18"/>
       <c r="DA77" s="18"/>
+      <c r="DB77" s="18"/>
     </row>
     <row r="78" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -14021,6 +14110,7 @@
       <c r="CY78" s="18"/>
       <c r="CZ78" s="18"/>
       <c r="DA78" s="18"/>
+      <c r="DB78" s="18"/>
     </row>
     <row r="79" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -14105,6 +14195,7 @@
       <c r="CY79" s="18"/>
       <c r="CZ79" s="18"/>
       <c r="DA79" s="18"/>
+      <c r="DB79" s="18"/>
     </row>
     <row r="80" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
@@ -14191,10 +14282,11 @@
       <c r="CY80" s="18"/>
       <c r="CZ80" s="18"/>
       <c r="DA80" s="18"/>
+      <c r="DB80" s="18"/>
     </row>
     <row r="81" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -14594,6 +14686,9 @@
       <c r="CY84" s="25"/>
       <c r="CZ84" s="25"/>
       <c r="DA84" s="25"/>
+      <c r="DB84" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="85" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -14910,6 +15005,9 @@
       </c>
       <c r="DA85" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB85" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15308,7 +15406,9 @@
       <c r="DA87" s="13">
         <v>142.96466325274881</v>
       </c>
-      <c r="DB87" s="20"/>
+      <c r="DB87" s="13">
+        <v>123.61978579132276</v>
+      </c>
       <c r="DC87" s="20"/>
       <c r="DD87" s="20"/>
       <c r="DE87" s="20"/>
@@ -15695,7 +15795,9 @@
       <c r="DA88" s="13">
         <v>130.03059961082388</v>
       </c>
-      <c r="DB88" s="20"/>
+      <c r="DB88" s="13">
+        <v>114.36304773982791</v>
+      </c>
       <c r="DC88" s="20"/>
       <c r="DD88" s="20"/>
       <c r="DE88" s="20"/>
@@ -15871,7 +15973,7 @@
       <c r="CY89" s="8"/>
       <c r="CZ89" s="8"/>
       <c r="DA89" s="8"/>
-      <c r="DB89" s="20"/>
+      <c r="DB89" s="8"/>
       <c r="DC89" s="20"/>
       <c r="DD89" s="20"/>
       <c r="DE89" s="20"/>
@@ -16258,7 +16360,9 @@
       <c r="DA90" s="13">
         <v>138.58236593565104</v>
       </c>
-      <c r="DB90" s="20"/>
+      <c r="DB90" s="13">
+        <v>120.56238349993838</v>
+      </c>
       <c r="DC90" s="20"/>
       <c r="DD90" s="20"/>
       <c r="DE90" s="20"/>
@@ -16435,6 +16539,7 @@
       <c r="CY91" s="10"/>
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
+      <c r="DB91" s="10"/>
     </row>
     <row r="92" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -16623,6 +16728,7 @@
       <c r="CY93" s="4"/>
       <c r="CZ93" s="4"/>
       <c r="DA93" s="4"/>
+      <c r="DB93" s="4"/>
     </row>
     <row r="94" spans="1:175" x14ac:dyDescent="0.25">
       <c r="B94" s="4"/>
@@ -16729,6 +16835,7 @@
       <c r="CY94" s="4"/>
       <c r="CZ94" s="4"/>
       <c r="DA94" s="4"/>
+      <c r="DB94" s="4"/>
     </row>
     <row r="95" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
@@ -16838,6 +16945,7 @@
       <c r="CY95" s="4"/>
       <c r="CZ95" s="4"/>
       <c r="DA95" s="4"/>
+      <c r="DB95" s="4"/>
     </row>
     <row r="96" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
@@ -16947,10 +17055,11 @@
       <c r="CY96" s="4"/>
       <c r="CZ96" s="4"/>
       <c r="DA96" s="4"/>
+      <c r="DB96" s="4"/>
     </row>
     <row r="97" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -17056,6 +17165,7 @@
       <c r="CY97" s="4"/>
       <c r="CZ97" s="4"/>
       <c r="DA97" s="4"/>
+      <c r="DB97" s="4"/>
     </row>
     <row r="98" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
@@ -17163,6 +17273,7 @@
       <c r="CY98" s="4"/>
       <c r="CZ98" s="4"/>
       <c r="DA98" s="4"/>
+      <c r="DB98" s="4"/>
     </row>
     <row r="99" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
@@ -17272,10 +17383,11 @@
       <c r="CY99" s="4"/>
       <c r="CZ99" s="4"/>
       <c r="DA99" s="4"/>
+      <c r="DB99" s="4"/>
     </row>
     <row r="100" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -17381,6 +17493,7 @@
       <c r="CY100" s="4"/>
       <c r="CZ100" s="4"/>
       <c r="DA100" s="4"/>
+      <c r="DB100" s="4"/>
     </row>
     <row r="101" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
@@ -17490,6 +17603,7 @@
       <c r="CY101" s="4"/>
       <c r="CZ101" s="4"/>
       <c r="DA101" s="4"/>
+      <c r="DB101" s="4"/>
     </row>
     <row r="102" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -17597,6 +17711,7 @@
       <c r="CY102" s="4"/>
       <c r="CZ102" s="4"/>
       <c r="DA102" s="4"/>
+      <c r="DB102" s="4"/>
     </row>
     <row r="103" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A103" s="14"/>
@@ -17756,6 +17871,9 @@
       <c r="CY103" s="25"/>
       <c r="CZ103" s="25"/>
       <c r="DA103" s="25"/>
+      <c r="DB103" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="104" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -18072,6 +18190,9 @@
       </c>
       <c r="DA104" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB104" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -18180,6 +18301,7 @@
       <c r="CY105" s="4"/>
       <c r="CZ105" s="4"/>
       <c r="DA105" s="4"/>
+      <c r="DB105" s="4"/>
     </row>
     <row r="106" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
@@ -18497,7 +18619,9 @@
       <c r="DA106" s="13">
         <v>68.208981697067244</v>
       </c>
-      <c r="DB106" s="20"/>
+      <c r="DB106" s="13">
+        <v>68.669414723168316</v>
+      </c>
       <c r="DC106" s="20"/>
       <c r="DD106" s="20"/>
       <c r="DE106" s="20"/>
@@ -18888,7 +19012,9 @@
       <c r="DA107" s="13">
         <v>31.791018302932766</v>
       </c>
-      <c r="DB107" s="20"/>
+      <c r="DB107" s="13">
+        <v>31.33058527683168</v>
+      </c>
       <c r="DC107" s="20"/>
       <c r="DD107" s="20"/>
       <c r="DE107" s="20"/>
@@ -19068,7 +19194,7 @@
       <c r="CY108" s="8"/>
       <c r="CZ108" s="8"/>
       <c r="DA108" s="8"/>
-      <c r="DB108" s="20"/>
+      <c r="DB108" s="8"/>
       <c r="DC108" s="20"/>
       <c r="DD108" s="20"/>
       <c r="DE108" s="20"/>
@@ -19459,7 +19585,9 @@
       <c r="DA109" s="13">
         <v>100</v>
       </c>
-      <c r="DB109" s="20"/>
+      <c r="DB109" s="13">
+        <v>100</v>
+      </c>
       <c r="DC109" s="20"/>
       <c r="DD109" s="20"/>
       <c r="DE109" s="20"/>
@@ -19640,6 +19768,7 @@
       <c r="CY110" s="10"/>
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
+      <c r="DB110" s="10"/>
     </row>
     <row r="111" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -19749,6 +19878,7 @@
       <c r="CY111" s="4"/>
       <c r="CZ111" s="4"/>
       <c r="DA111" s="4"/>
+      <c r="DB111" s="4"/>
     </row>
     <row r="112" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="8"/>
@@ -19855,7 +19985,7 @@
       <c r="CY112" s="8"/>
       <c r="CZ112" s="8"/>
       <c r="DA112" s="8"/>
-      <c r="DB112" s="20"/>
+      <c r="DB112" s="8"/>
       <c r="DC112" s="20"/>
       <c r="DD112" s="20"/>
       <c r="DE112" s="20"/>
@@ -20035,7 +20165,7 @@
       <c r="CY113" s="8"/>
       <c r="CZ113" s="8"/>
       <c r="DA113" s="8"/>
-      <c r="DB113" s="20"/>
+      <c r="DB113" s="8"/>
       <c r="DC113" s="20"/>
       <c r="DD113" s="20"/>
       <c r="DE113" s="20"/>
@@ -20218,6 +20348,7 @@
       <c r="CY114" s="4"/>
       <c r="CZ114" s="4"/>
       <c r="DA114" s="4"/>
+      <c r="DB114" s="4"/>
     </row>
     <row r="115" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
@@ -20327,10 +20458,11 @@
       <c r="CY115" s="4"/>
       <c r="CZ115" s="4"/>
       <c r="DA115" s="4"/>
+      <c r="DB115" s="4"/>
     </row>
     <row r="116" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -20436,6 +20568,7 @@
       <c r="CY116" s="4"/>
       <c r="CZ116" s="4"/>
       <c r="DA116" s="4"/>
+      <c r="DB116" s="4"/>
     </row>
     <row r="117" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
@@ -20543,6 +20676,7 @@
       <c r="CY117" s="4"/>
       <c r="CZ117" s="4"/>
       <c r="DA117" s="4"/>
+      <c r="DB117" s="4"/>
     </row>
     <row r="118" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
@@ -20652,10 +20786,11 @@
       <c r="CY118" s="4"/>
       <c r="CZ118" s="4"/>
       <c r="DA118" s="4"/>
+      <c r="DB118" s="4"/>
     </row>
     <row r="119" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -20761,6 +20896,7 @@
       <c r="CY119" s="4"/>
       <c r="CZ119" s="4"/>
       <c r="DA119" s="4"/>
+      <c r="DB119" s="4"/>
     </row>
     <row r="120" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
@@ -20870,6 +21006,7 @@
       <c r="CY120" s="4"/>
       <c r="CZ120" s="4"/>
       <c r="DA120" s="4"/>
+      <c r="DB120" s="4"/>
     </row>
     <row r="121" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
@@ -20977,6 +21114,7 @@
       <c r="CY121" s="4"/>
       <c r="CZ121" s="4"/>
       <c r="DA121" s="4"/>
+      <c r="DB121" s="4"/>
     </row>
     <row r="122" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A122" s="14"/>
@@ -21136,6 +21274,9 @@
       <c r="CY122" s="25"/>
       <c r="CZ122" s="25"/>
       <c r="DA122" s="25"/>
+      <c r="DB122" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="123" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -21452,6 +21593,9 @@
       </c>
       <c r="DA123" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB123" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -21560,6 +21704,7 @@
       <c r="CY124" s="4"/>
       <c r="CZ124" s="4"/>
       <c r="DA124" s="4"/>
+      <c r="DB124" s="4"/>
     </row>
     <row r="125" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
@@ -21877,7 +22022,9 @@
       <c r="DA125" s="13">
         <v>66.118171068117761</v>
       </c>
-      <c r="DB125" s="20"/>
+      <c r="DB125" s="13">
+        <v>66.971061788978275</v>
+      </c>
       <c r="DC125" s="20"/>
       <c r="DD125" s="20"/>
       <c r="DE125" s="20"/>
@@ -22268,7 +22415,9 @@
       <c r="DA126" s="13">
         <v>33.881828931882239</v>
       </c>
-      <c r="DB126" s="20"/>
+      <c r="DB126" s="13">
+        <v>33.028938211021732</v>
+      </c>
       <c r="DC126" s="20"/>
       <c r="DD126" s="20"/>
       <c r="DE126" s="20"/>
@@ -22448,7 +22597,7 @@
       <c r="CY127" s="8"/>
       <c r="CZ127" s="8"/>
       <c r="DA127" s="8"/>
-      <c r="DB127" s="20"/>
+      <c r="DB127" s="8"/>
       <c r="DC127" s="20"/>
       <c r="DD127" s="20"/>
       <c r="DE127" s="20"/>
@@ -22839,7 +22988,9 @@
       <c r="DA128" s="13">
         <v>100</v>
       </c>
-      <c r="DB128" s="20"/>
+      <c r="DB128" s="13">
+        <v>100</v>
+      </c>
       <c r="DC128" s="20"/>
       <c r="DD128" s="20"/>
       <c r="DE128" s="20"/>
@@ -22914,7 +23065,7 @@
       <c r="FV128" s="20"/>
       <c r="FW128" s="20"/>
     </row>
-    <row r="129" spans="1:105" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:106" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="10"/>
@@ -23020,8 +23171,9 @@
       <c r="CY129" s="10"/>
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
+      <c r="DB129" s="10"/>
     </row>
-    <row r="130" spans="1:105" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:106" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
         <v>6</v>
       </c>
@@ -23129,14 +23281,16 @@
       <c r="CY130" s="4"/>
       <c r="CZ130" s="4"/>
       <c r="DA130" s="4"/>
+      <c r="DB130" s="4"/>
     </row>
-    <row r="131" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CX131" s="23"/>
       <c r="CY131" s="23"/>
       <c r="CZ131" s="23"/>
       <c r="DA131" s="23"/>
+      <c r="DB131" s="23"/>
     </row>
-    <row r="132" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT132" s="24"/>
       <c r="CU132" s="24"/>
       <c r="CV132" s="24"/>
@@ -23144,8 +23298,9 @@
       <c r="CY132" s="24"/>
       <c r="CZ132" s="24"/>
       <c r="DA132" s="24"/>
+      <c r="DB132" s="24"/>
     </row>
-    <row r="133" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT133" s="24"/>
       <c r="CU133" s="24"/>
       <c r="CV133" s="24"/>
@@ -23153,8 +23308,9 @@
       <c r="CY133" s="24"/>
       <c r="CZ133" s="24"/>
       <c r="DA133" s="24"/>
+      <c r="DB133" s="24"/>
     </row>
-    <row r="134" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT134" s="24"/>
       <c r="CU134" s="24"/>
       <c r="CV134" s="24"/>
@@ -23162,8 +23318,9 @@
       <c r="CY134" s="24"/>
       <c r="CZ134" s="24"/>
       <c r="DA134" s="24"/>
+      <c r="DB134" s="24"/>
     </row>
-    <row r="135" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT135" s="24"/>
       <c r="CU135" s="24"/>
       <c r="CV135" s="24"/>
@@ -23171,8 +23328,9 @@
       <c r="CY135" s="24"/>
       <c r="CZ135" s="24"/>
       <c r="DA135" s="24"/>
+      <c r="DB135" s="24"/>
     </row>
-    <row r="136" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT136" s="24"/>
       <c r="CU136" s="24"/>
       <c r="CV136" s="24"/>
@@ -23180,8 +23338,9 @@
       <c r="CY136" s="24"/>
       <c r="CZ136" s="24"/>
       <c r="DA136" s="24"/>
+      <c r="DB136" s="24"/>
     </row>
-    <row r="137" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT137" s="24"/>
       <c r="CU137" s="24"/>
       <c r="CV137" s="24"/>
@@ -23189,8 +23348,9 @@
       <c r="CY137" s="24"/>
       <c r="CZ137" s="24"/>
       <c r="DA137" s="24"/>
+      <c r="DB137" s="24"/>
     </row>
-    <row r="138" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT138" s="24"/>
       <c r="CU138" s="24"/>
       <c r="CV138" s="24"/>
@@ -23198,8 +23358,9 @@
       <c r="CY138" s="24"/>
       <c r="CZ138" s="24"/>
       <c r="DA138" s="24"/>
+      <c r="DB138" s="24"/>
     </row>
-    <row r="139" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT139" s="24"/>
       <c r="CU139" s="24"/>
       <c r="CV139" s="24"/>
@@ -23207,8 +23368,9 @@
       <c r="CY139" s="24"/>
       <c r="CZ139" s="24"/>
       <c r="DA139" s="24"/>
+      <c r="DB139" s="24"/>
     </row>
-    <row r="140" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT140" s="24"/>
       <c r="CU140" s="24"/>
       <c r="CV140" s="24"/>
@@ -23216,8 +23378,9 @@
       <c r="CY140" s="24"/>
       <c r="CZ140" s="24"/>
       <c r="DA140" s="24"/>
+      <c r="DB140" s="24"/>
     </row>
-    <row r="141" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT141" s="24"/>
       <c r="CU141" s="24"/>
       <c r="CV141" s="24"/>
@@ -23225,8 +23388,9 @@
       <c r="CY141" s="24"/>
       <c r="CZ141" s="24"/>
       <c r="DA141" s="24"/>
+      <c r="DB141" s="24"/>
     </row>
-    <row r="142" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT142" s="24"/>
       <c r="CU142" s="24"/>
       <c r="CV142" s="24"/>
@@ -23234,8 +23398,9 @@
       <c r="CY142" s="24"/>
       <c r="CZ142" s="24"/>
       <c r="DA142" s="24"/>
+      <c r="DB142" s="24"/>
     </row>
-    <row r="143" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT143" s="24"/>
       <c r="CU143" s="24"/>
       <c r="CV143" s="24"/>
@@ -23243,8 +23408,9 @@
       <c r="CY143" s="24"/>
       <c r="CZ143" s="24"/>
       <c r="DA143" s="24"/>
+      <c r="DB143" s="24"/>
     </row>
-    <row r="144" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT144" s="24"/>
       <c r="CU144" s="24"/>
       <c r="CV144" s="24"/>
@@ -23252,8 +23418,9 @@
       <c r="CY144" s="24"/>
       <c r="CZ144" s="24"/>
       <c r="DA144" s="24"/>
+      <c r="DB144" s="24"/>
     </row>
-    <row r="145" spans="98:105" x14ac:dyDescent="0.25">
+    <row r="145" spans="98:106" x14ac:dyDescent="0.25">
       <c r="CT145" s="24"/>
       <c r="CU145" s="24"/>
       <c r="CV145" s="24"/>
@@ -23261,8 +23428,9 @@
       <c r="CY145" s="24"/>
       <c r="CZ145" s="24"/>
       <c r="DA145" s="24"/>
+      <c r="DB145" s="24"/>
     </row>
-    <row r="146" spans="98:105" x14ac:dyDescent="0.25">
+    <row r="146" spans="98:106" x14ac:dyDescent="0.25">
       <c r="CT146" s="24"/>
       <c r="CU146" s="24"/>
       <c r="CV146" s="24"/>
@@ -23270,8 +23438,9 @@
       <c r="CY146" s="24"/>
       <c r="CZ146" s="24"/>
       <c r="DA146" s="24"/>
+      <c r="DB146" s="24"/>
     </row>
-    <row r="147" spans="98:105" x14ac:dyDescent="0.25">
+    <row r="147" spans="98:106" x14ac:dyDescent="0.25">
       <c r="CT147" s="24"/>
       <c r="CU147" s="24"/>
       <c r="CV147" s="24"/>
@@ -23279,8 +23448,9 @@
       <c r="CY147" s="24"/>
       <c r="CZ147" s="24"/>
       <c r="DA147" s="24"/>
+      <c r="DB147" s="24"/>
     </row>
-    <row r="148" spans="98:105" x14ac:dyDescent="0.25">
+    <row r="148" spans="98:106" x14ac:dyDescent="0.25">
       <c r="CT148" s="24"/>
       <c r="CU148" s="24"/>
       <c r="CV148" s="24"/>
@@ -23295,9 +23465,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="81" man="1"/>
-    <brk id="76" max="81" man="1"/>
-    <brk id="94" max="81" man="1"/>
+    <brk id="38" max="105" man="1"/>
+    <brk id="76" max="105" man="1"/>
+    <brk id="94" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-19EDUC_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-19EDUC_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C0EC8C-74C3-4DD5-B1B0-54A1116C6416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D21816-85E6-445D-94D5-C3A506CE4126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">EDUC!$A$1:$DB$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">EDUC!$A$1:$DC$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -682,13 +682,13 @@
     <t>Table 20.7 Gross Value Added in Education, by Industry</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1216,8 +1216,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="4" customWidth="1"/>
-    <col min="2" max="106" width="13" style="21" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="21"/>
+    <col min="2" max="107" width="13" style="21" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="3" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="6" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1360,6 +1360,7 @@
       <c r="CZ8" s="4"/>
       <c r="DA8" s="4"/>
       <c r="DB8" s="4"/>
+      <c r="DC8" s="4"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
@@ -1522,6 +1523,7 @@
       <c r="DB9" s="25">
         <v>2026</v>
       </c>
+      <c r="DC9" s="25"/>
     </row>
     <row r="10" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1841,6 +1843,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1950,6 +1955,7 @@
       <c r="CZ11" s="4"/>
       <c r="DA11" s="4"/>
       <c r="DB11" s="4"/>
+      <c r="DC11" s="4"/>
     </row>
     <row r="12" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2270,7 +2276,9 @@
       <c r="DB12" s="26">
         <v>209966.11300975404</v>
       </c>
-      <c r="DC12" s="20"/>
+      <c r="DC12" s="26">
+        <v>280350.64302513376</v>
+      </c>
       <c r="DD12" s="20"/>
       <c r="DE12" s="20"/>
       <c r="DF12" s="20"/>
@@ -2661,9 +2669,11 @@
         <v>98227.690031028469</v>
       </c>
       <c r="DB13" s="26">
-        <v>95797.542987904744</v>
-      </c>
-      <c r="DC13" s="20"/>
+        <v>95157.369448560217</v>
+      </c>
+      <c r="DC13" s="26">
+        <v>101617.96576655746</v>
+      </c>
       <c r="DD13" s="20"/>
       <c r="DE13" s="20"/>
       <c r="DF13" s="20"/>
@@ -2843,7 +2853,7 @@
       <c r="CZ14" s="8"/>
       <c r="DA14" s="8"/>
       <c r="DB14" s="8"/>
-      <c r="DC14" s="20"/>
+      <c r="DC14" s="8"/>
       <c r="DD14" s="20"/>
       <c r="DE14" s="20"/>
       <c r="DF14" s="20"/>
@@ -3234,9 +3244,11 @@
         <v>308979.37617168692</v>
       </c>
       <c r="DB15" s="16">
-        <v>305763.65599765879</v>
-      </c>
-      <c r="DC15" s="20"/>
+        <v>305123.48245831428</v>
+      </c>
+      <c r="DC15" s="16">
+        <v>381968.60879169125</v>
+      </c>
       <c r="DD15" s="20"/>
       <c r="DE15" s="20"/>
       <c r="DF15" s="20"/>
@@ -3417,6 +3429,7 @@
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
       <c r="DB16" s="10"/>
+      <c r="DC16" s="10"/>
     </row>
     <row r="17" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3527,6 +3540,7 @@
       <c r="CZ17" s="4"/>
       <c r="DA17" s="4"/>
       <c r="DB17" s="4"/>
+      <c r="DC17" s="4"/>
     </row>
     <row r="18" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="8"/>
@@ -3634,7 +3648,7 @@
       <c r="CZ18" s="8"/>
       <c r="DA18" s="8"/>
       <c r="DB18" s="8"/>
-      <c r="DC18" s="20"/>
+      <c r="DC18" s="8"/>
       <c r="DD18" s="20"/>
       <c r="DE18" s="20"/>
       <c r="DF18" s="20"/>
@@ -3814,7 +3828,7 @@
       <c r="CZ19" s="8"/>
       <c r="DA19" s="8"/>
       <c r="DB19" s="8"/>
-      <c r="DC19" s="20"/>
+      <c r="DC19" s="8"/>
       <c r="DD19" s="20"/>
       <c r="DE19" s="20"/>
       <c r="DF19" s="20"/>
@@ -3997,6 +4011,7 @@
       <c r="CZ20" s="4"/>
       <c r="DA20" s="4"/>
       <c r="DB20" s="4"/>
+      <c r="DC20" s="4"/>
     </row>
     <row r="21" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -4107,10 +4122,11 @@
       <c r="CZ21" s="4"/>
       <c r="DA21" s="4"/>
       <c r="DB21" s="4"/>
+      <c r="DC21" s="4"/>
     </row>
     <row r="22" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4217,6 +4233,7 @@
       <c r="CZ22" s="4"/>
       <c r="DA22" s="4"/>
       <c r="DB22" s="4"/>
+      <c r="DC22" s="4"/>
     </row>
     <row r="23" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
@@ -4325,6 +4342,7 @@
       <c r="CZ23" s="4"/>
       <c r="DA23" s="4"/>
       <c r="DB23" s="4"/>
+      <c r="DC23" s="4"/>
     </row>
     <row r="24" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
@@ -4435,10 +4453,11 @@
       <c r="CZ24" s="4"/>
       <c r="DA24" s="4"/>
       <c r="DB24" s="4"/>
+      <c r="DC24" s="4"/>
     </row>
     <row r="25" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -4545,6 +4564,7 @@
       <c r="CZ25" s="4"/>
       <c r="DA25" s="4"/>
       <c r="DB25" s="4"/>
+      <c r="DC25" s="4"/>
     </row>
     <row r="26" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -4655,6 +4675,7 @@
       <c r="CZ26" s="4"/>
       <c r="DA26" s="4"/>
       <c r="DB26" s="4"/>
+      <c r="DC26" s="4"/>
     </row>
     <row r="27" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
@@ -4763,6 +4784,7 @@
       <c r="CZ27" s="4"/>
       <c r="DA27" s="4"/>
       <c r="DB27" s="4"/>
+      <c r="DC27" s="4"/>
     </row>
     <row r="28" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
@@ -4925,6 +4947,7 @@
       <c r="DB28" s="25">
         <v>2026</v>
       </c>
+      <c r="DC28" s="25"/>
     </row>
     <row r="29" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -5244,6 +5267,9 @@
       </c>
       <c r="DB29" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC29" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5353,6 +5379,7 @@
       <c r="CZ30" s="4"/>
       <c r="DA30" s="4"/>
       <c r="DB30" s="4"/>
+      <c r="DC30" s="4"/>
     </row>
     <row r="31" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
@@ -5673,7 +5700,9 @@
       <c r="DB31" s="26">
         <v>169848.30677848676</v>
       </c>
-      <c r="DC31" s="20"/>
+      <c r="DC31" s="26">
+        <v>225975.12143282409</v>
+      </c>
       <c r="DD31" s="20"/>
       <c r="DE31" s="20"/>
       <c r="DF31" s="20"/>
@@ -6064,9 +6093,11 @@
         <v>75541.980368482356</v>
       </c>
       <c r="DB32" s="26">
-        <v>83766.168252039715</v>
-      </c>
-      <c r="DC32" s="20"/>
+        <v>83206.49400383867</v>
+      </c>
+      <c r="DC32" s="26">
+        <v>86801.195133803063</v>
+      </c>
       <c r="DD32" s="20"/>
       <c r="DE32" s="20"/>
       <c r="DF32" s="20"/>
@@ -6246,7 +6277,7 @@
       <c r="CZ33" s="8"/>
       <c r="DA33" s="8"/>
       <c r="DB33" s="8"/>
-      <c r="DC33" s="20"/>
+      <c r="DC33" s="8"/>
       <c r="DD33" s="20"/>
       <c r="DE33" s="20"/>
       <c r="DF33" s="20"/>
@@ -6637,9 +6668,11 @@
         <v>222957.20966054051</v>
       </c>
       <c r="DB34" s="16">
-        <v>253614.47503052646</v>
-      </c>
-      <c r="DC34" s="20"/>
+        <v>253054.80078232544</v>
+      </c>
+      <c r="DC34" s="16">
+        <v>312776.31656662712</v>
+      </c>
       <c r="DD34" s="20"/>
       <c r="DE34" s="20"/>
       <c r="DF34" s="20"/>
@@ -6820,6 +6853,7 @@
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
       <c r="DB35" s="10"/>
+      <c r="DC35" s="10"/>
     </row>
     <row r="36" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -6930,6 +6964,7 @@
       <c r="CZ36" s="4"/>
       <c r="DA36" s="4"/>
       <c r="DB36" s="4"/>
+      <c r="DC36" s="4"/>
     </row>
     <row r="37" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8"/>
@@ -7037,7 +7072,7 @@
       <c r="CZ37" s="8"/>
       <c r="DA37" s="8"/>
       <c r="DB37" s="8"/>
-      <c r="DC37" s="20"/>
+      <c r="DC37" s="8"/>
       <c r="DD37" s="20"/>
       <c r="DE37" s="20"/>
       <c r="DF37" s="20"/>
@@ -7217,7 +7252,7 @@
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
       <c r="DB38" s="7"/>
-      <c r="DC38" s="20"/>
+      <c r="DC38" s="7"/>
       <c r="DD38" s="20"/>
       <c r="DE38" s="20"/>
       <c r="DF38" s="20"/>
@@ -7400,6 +7435,7 @@
       <c r="CZ39" s="27"/>
       <c r="DA39" s="27"/>
       <c r="DB39" s="27"/>
+      <c r="DC39" s="27"/>
     </row>
     <row r="40" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
@@ -7510,10 +7546,11 @@
       <c r="CZ40" s="27"/>
       <c r="DA40" s="27"/>
       <c r="DB40" s="27"/>
+      <c r="DC40" s="27"/>
     </row>
     <row r="41" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -7620,6 +7657,7 @@
       <c r="CZ41" s="27"/>
       <c r="DA41" s="27"/>
       <c r="DB41" s="27"/>
+      <c r="DC41" s="27"/>
     </row>
     <row r="42" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
@@ -7728,6 +7766,7 @@
       <c r="CZ42" s="27"/>
       <c r="DA42" s="27"/>
       <c r="DB42" s="27"/>
+      <c r="DC42" s="27"/>
     </row>
     <row r="43" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
@@ -7838,10 +7877,11 @@
       <c r="CZ43" s="27"/>
       <c r="DA43" s="27"/>
       <c r="DB43" s="27"/>
+      <c r="DC43" s="27"/>
     </row>
     <row r="44" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -7927,6 +7967,7 @@
       <c r="CZ44" s="18"/>
       <c r="DA44" s="18"/>
       <c r="DB44" s="18"/>
+      <c r="DC44" s="18"/>
     </row>
     <row r="45" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
@@ -8014,6 +8055,7 @@
       <c r="CZ45" s="18"/>
       <c r="DA45" s="18"/>
       <c r="DB45" s="18"/>
+      <c r="DC45" s="18"/>
     </row>
     <row r="46" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
@@ -8118,10 +8160,11 @@
       <c r="CV46" s="4"/>
       <c r="CW46" s="4"/>
       <c r="CX46" s="4"/>
-      <c r="CY46" s="27"/>
+      <c r="CY46" s="4"/>
       <c r="CZ46" s="27"/>
       <c r="DA46" s="27"/>
       <c r="DB46" s="27"/>
+      <c r="DC46" s="27"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="14"/>
@@ -8276,12 +8319,13 @@
       <c r="CV47" s="25"/>
       <c r="CW47" s="25"/>
       <c r="CX47" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY47" s="28"/>
+        <v>51</v>
+      </c>
+      <c r="CY47" s="25"/>
       <c r="CZ47" s="28"/>
       <c r="DA47" s="28"/>
       <c r="DB47" s="28"/>
+      <c r="DC47" s="28"/>
     </row>
     <row r="48" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -8590,10 +8634,13 @@
       <c r="CX48" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY48" s="29"/>
+      <c r="CY48" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ48" s="29"/>
       <c r="DA48" s="29"/>
       <c r="DB48" s="29"/>
+      <c r="DC48" s="29"/>
     </row>
     <row r="49" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
@@ -8698,10 +8745,11 @@
       <c r="CV49" s="4"/>
       <c r="CW49" s="4"/>
       <c r="CX49" s="4"/>
-      <c r="CY49" s="27"/>
+      <c r="CY49" s="4"/>
       <c r="CZ49" s="27"/>
       <c r="DA49" s="27"/>
       <c r="DB49" s="27"/>
+      <c r="DC49" s="27"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -9010,11 +9058,13 @@
       <c r="CX50" s="13">
         <v>10.905053430564294</v>
       </c>
-      <c r="CY50" s="15"/>
+      <c r="CY50" s="13">
+        <v>21.369355616195577</v>
+      </c>
       <c r="CZ50" s="15"/>
       <c r="DA50" s="15"/>
       <c r="DB50" s="15"/>
-      <c r="DC50" s="20"/>
+      <c r="DC50" s="15"/>
       <c r="DD50" s="20"/>
       <c r="DE50" s="20"/>
       <c r="DF50" s="20"/>
@@ -9389,13 +9439,15 @@
         <v>11.3510483315399</v>
       </c>
       <c r="CX51" s="13">
-        <v>8.3124010172558371</v>
-      </c>
-      <c r="CY51" s="15"/>
+        <v>7.588596095423199</v>
+      </c>
+      <c r="CY51" s="13">
+        <v>6.0018863433888328</v>
+      </c>
       <c r="CZ51" s="15"/>
       <c r="DA51" s="15"/>
       <c r="DB51" s="15"/>
-      <c r="DC51" s="20"/>
+      <c r="DC51" s="15"/>
       <c r="DD51" s="20"/>
       <c r="DE51" s="20"/>
       <c r="DF51" s="20"/>
@@ -9568,11 +9620,11 @@
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
       <c r="CX52" s="8"/>
-      <c r="CY52" s="7"/>
+      <c r="CY52" s="8"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
       <c r="DB52" s="7"/>
-      <c r="DC52" s="20"/>
+      <c r="DC52" s="7"/>
       <c r="DD52" s="20"/>
       <c r="DE52" s="20"/>
       <c r="DF52" s="20"/>
@@ -9947,13 +9999,15 @@
         <v>9.3372433361709568</v>
       </c>
       <c r="CX53" s="13">
-        <v>10.079507767662889</v>
-      </c>
-      <c r="CY53" s="15"/>
+        <v>9.8490356801056009</v>
+      </c>
+      <c r="CY53" s="13">
+        <v>16.862169137974973</v>
+      </c>
       <c r="CZ53" s="15"/>
       <c r="DA53" s="15"/>
       <c r="DB53" s="15"/>
-      <c r="DC53" s="20"/>
+      <c r="DC53" s="15"/>
       <c r="DD53" s="20"/>
       <c r="DE53" s="20"/>
       <c r="DF53" s="20"/>
@@ -10126,10 +10180,11 @@
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
       <c r="CX54" s="10"/>
-      <c r="CY54" s="30"/>
+      <c r="CY54" s="10"/>
       <c r="CZ54" s="30"/>
       <c r="DA54" s="30"/>
       <c r="DB54" s="30"/>
+      <c r="DC54" s="30"/>
     </row>
     <row r="55" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
@@ -10236,10 +10291,11 @@
       <c r="CV55" s="4"/>
       <c r="CW55" s="4"/>
       <c r="CX55" s="4"/>
-      <c r="CY55" s="27"/>
+      <c r="CY55" s="4"/>
       <c r="CZ55" s="27"/>
       <c r="DA55" s="27"/>
       <c r="DB55" s="27"/>
+      <c r="DC55" s="27"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="8"/>
@@ -10343,11 +10399,11 @@
       <c r="CV56" s="8"/>
       <c r="CW56" s="8"/>
       <c r="CX56" s="8"/>
-      <c r="CY56" s="7"/>
+      <c r="CY56" s="8"/>
       <c r="CZ56" s="7"/>
       <c r="DA56" s="7"/>
       <c r="DB56" s="7"/>
-      <c r="DC56" s="20"/>
+      <c r="DC56" s="7"/>
       <c r="DD56" s="20"/>
       <c r="DE56" s="20"/>
       <c r="DF56" s="20"/>
@@ -10519,11 +10575,11 @@
       <c r="CV57" s="8"/>
       <c r="CW57" s="8"/>
       <c r="CX57" s="8"/>
-      <c r="CY57" s="7"/>
+      <c r="CY57" s="8"/>
       <c r="CZ57" s="7"/>
       <c r="DA57" s="7"/>
       <c r="DB57" s="7"/>
-      <c r="DC57" s="20"/>
+      <c r="DC57" s="7"/>
       <c r="DD57" s="20"/>
       <c r="DE57" s="20"/>
       <c r="DF57" s="20"/>
@@ -10698,10 +10754,11 @@
       <c r="CV58" s="4"/>
       <c r="CW58" s="4"/>
       <c r="CX58" s="4"/>
-      <c r="CY58" s="27"/>
+      <c r="CY58" s="4"/>
       <c r="CZ58" s="27"/>
       <c r="DA58" s="27"/>
       <c r="DB58" s="27"/>
+      <c r="DC58" s="27"/>
     </row>
     <row r="59" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
@@ -10808,14 +10865,15 @@
       <c r="CV59" s="4"/>
       <c r="CW59" s="4"/>
       <c r="CX59" s="4"/>
-      <c r="CY59" s="27"/>
+      <c r="CY59" s="4"/>
       <c r="CZ59" s="27"/>
       <c r="DA59" s="27"/>
       <c r="DB59" s="27"/>
+      <c r="DC59" s="27"/>
     </row>
     <row r="60" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -10918,10 +10976,11 @@
       <c r="CV60" s="4"/>
       <c r="CW60" s="4"/>
       <c r="CX60" s="4"/>
-      <c r="CY60" s="27"/>
+      <c r="CY60" s="4"/>
       <c r="CZ60" s="27"/>
       <c r="DA60" s="27"/>
       <c r="DB60" s="27"/>
+      <c r="DC60" s="27"/>
     </row>
     <row r="61" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
@@ -11026,10 +11085,11 @@
       <c r="CV61" s="4"/>
       <c r="CW61" s="4"/>
       <c r="CX61" s="4"/>
-      <c r="CY61" s="27"/>
+      <c r="CY61" s="4"/>
       <c r="CZ61" s="27"/>
       <c r="DA61" s="27"/>
       <c r="DB61" s="27"/>
+      <c r="DC61" s="27"/>
     </row>
     <row r="62" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
@@ -11136,14 +11196,15 @@
       <c r="CV62" s="4"/>
       <c r="CW62" s="4"/>
       <c r="CX62" s="4"/>
-      <c r="CY62" s="27"/>
+      <c r="CY62" s="4"/>
       <c r="CZ62" s="27"/>
       <c r="DA62" s="27"/>
       <c r="DB62" s="27"/>
+      <c r="DC62" s="27"/>
     </row>
     <row r="63" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -11246,10 +11307,11 @@
       <c r="CV63" s="4"/>
       <c r="CW63" s="4"/>
       <c r="CX63" s="4"/>
-      <c r="CY63" s="27"/>
+      <c r="CY63" s="4"/>
       <c r="CZ63" s="27"/>
       <c r="DA63" s="27"/>
       <c r="DB63" s="27"/>
+      <c r="DC63" s="27"/>
     </row>
     <row r="64" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
@@ -11356,10 +11418,11 @@
       <c r="CV64" s="4"/>
       <c r="CW64" s="4"/>
       <c r="CX64" s="4"/>
-      <c r="CY64" s="27"/>
+      <c r="CY64" s="4"/>
       <c r="CZ64" s="27"/>
       <c r="DA64" s="27"/>
       <c r="DB64" s="27"/>
+      <c r="DC64" s="27"/>
     </row>
     <row r="65" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
@@ -11464,10 +11527,11 @@
       <c r="CV65" s="4"/>
       <c r="CW65" s="4"/>
       <c r="CX65" s="4"/>
-      <c r="CY65" s="27"/>
+      <c r="CY65" s="4"/>
       <c r="CZ65" s="27"/>
       <c r="DA65" s="27"/>
       <c r="DB65" s="27"/>
+      <c r="DC65" s="27"/>
     </row>
     <row r="66" spans="1:175" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="14"/>
@@ -11622,12 +11686,13 @@
       <c r="CV66" s="25"/>
       <c r="CW66" s="25"/>
       <c r="CX66" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="28"/>
+        <v>51</v>
+      </c>
+      <c r="CY66" s="25"/>
       <c r="CZ66" s="28"/>
       <c r="DA66" s="28"/>
       <c r="DB66" s="28"/>
+      <c r="DC66" s="28"/>
     </row>
     <row r="67" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -11936,10 +12001,13 @@
       <c r="CX67" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY67" s="29"/>
+      <c r="CY67" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ67" s="29"/>
       <c r="DA67" s="29"/>
       <c r="DB67" s="29"/>
+      <c r="DC67" s="29"/>
     </row>
     <row r="68" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
@@ -12044,10 +12112,11 @@
       <c r="CV68" s="4"/>
       <c r="CW68" s="4"/>
       <c r="CX68" s="4"/>
-      <c r="CY68" s="27"/>
+      <c r="CY68" s="4"/>
       <c r="CZ68" s="27"/>
       <c r="DA68" s="27"/>
       <c r="DB68" s="27"/>
+      <c r="DC68" s="27"/>
     </row>
     <row r="69" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
@@ -12356,11 +12425,13 @@
       <c r="CX69" s="13">
         <v>6.6347156014135606</v>
       </c>
-      <c r="CY69" s="15"/>
+      <c r="CY69" s="13">
+        <v>16.988592863649316</v>
+      </c>
       <c r="CZ69" s="15"/>
       <c r="DA69" s="15"/>
       <c r="DB69" s="15"/>
-      <c r="DC69" s="20"/>
+      <c r="DC69" s="15"/>
       <c r="DD69" s="20"/>
       <c r="DE69" s="20"/>
       <c r="DF69" s="20"/>
@@ -12735,13 +12806,15 @@
         <v>7.6189300784676561</v>
       </c>
       <c r="CX70" s="13">
-        <v>5.0446448671107191</v>
-      </c>
-      <c r="CY70" s="15"/>
+        <v>4.3428008664796494</v>
+      </c>
+      <c r="CY70" s="13">
+        <v>2.9570300521535557</v>
+      </c>
       <c r="CZ70" s="15"/>
       <c r="DA70" s="15"/>
       <c r="DB70" s="15"/>
-      <c r="DC70" s="20"/>
+      <c r="DC70" s="15"/>
       <c r="DD70" s="20"/>
       <c r="DE70" s="20"/>
       <c r="DF70" s="20"/>
@@ -12913,11 +12986,11 @@
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
       <c r="CX71" s="8"/>
-      <c r="CY71" s="7"/>
+      <c r="CY71" s="8"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
       <c r="DB71" s="7"/>
-      <c r="DC71" s="20"/>
+      <c r="DC71" s="7"/>
       <c r="DD71" s="20"/>
       <c r="DE71" s="20"/>
       <c r="DF71" s="20"/>
@@ -13292,13 +13365,15 @@
         <v>5.3406677613486693</v>
       </c>
       <c r="CX72" s="13">
-        <v>6.1042345734367842</v>
-      </c>
-      <c r="CY72" s="15"/>
+        <v>5.8700846586549744</v>
+      </c>
+      <c r="CY72" s="13">
+        <v>12.725128648580835</v>
+      </c>
       <c r="CZ72" s="15"/>
       <c r="DA72" s="15"/>
       <c r="DB72" s="15"/>
-      <c r="DC72" s="20"/>
+      <c r="DC72" s="15"/>
       <c r="DD72" s="20"/>
       <c r="DE72" s="20"/>
       <c r="DF72" s="20"/>
@@ -13471,10 +13546,11 @@
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
       <c r="CX73" s="10"/>
-      <c r="CY73" s="30"/>
+      <c r="CY73" s="10"/>
       <c r="CZ73" s="30"/>
       <c r="DA73" s="30"/>
       <c r="DB73" s="30"/>
+      <c r="DC73" s="30"/>
     </row>
     <row r="74" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
@@ -13581,10 +13657,11 @@
       <c r="CV74" s="4"/>
       <c r="CW74" s="4"/>
       <c r="CX74" s="4"/>
-      <c r="CY74" s="27"/>
+      <c r="CY74" s="4"/>
       <c r="CZ74" s="27"/>
       <c r="DA74" s="27"/>
       <c r="DB74" s="27"/>
+      <c r="DC74" s="27"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="8"/>
@@ -13692,7 +13769,7 @@
       <c r="CZ75" s="19"/>
       <c r="DA75" s="19"/>
       <c r="DB75" s="7"/>
-      <c r="DC75" s="20"/>
+      <c r="DC75" s="7"/>
       <c r="DD75" s="20"/>
       <c r="DE75" s="20"/>
       <c r="DF75" s="20"/>
@@ -13868,7 +13945,7 @@
       <c r="CZ76" s="19"/>
       <c r="DA76" s="19"/>
       <c r="DB76" s="19"/>
-      <c r="DC76" s="20"/>
+      <c r="DC76" s="19"/>
       <c r="DD76" s="20"/>
       <c r="DE76" s="20"/>
       <c r="DF76" s="20"/>
@@ -14024,10 +14101,11 @@
       <c r="CZ77" s="18"/>
       <c r="DA77" s="18"/>
       <c r="DB77" s="18"/>
+      <c r="DC77" s="18"/>
     </row>
     <row r="78" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -14111,6 +14189,7 @@
       <c r="CZ78" s="18"/>
       <c r="DA78" s="18"/>
       <c r="DB78" s="18"/>
+      <c r="DC78" s="18"/>
     </row>
     <row r="79" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -14196,6 +14275,7 @@
       <c r="CZ79" s="18"/>
       <c r="DA79" s="18"/>
       <c r="DB79" s="18"/>
+      <c r="DC79" s="18"/>
     </row>
     <row r="80" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
@@ -14283,10 +14363,11 @@
       <c r="CZ80" s="18"/>
       <c r="DA80" s="18"/>
       <c r="DB80" s="18"/>
+      <c r="DC80" s="18"/>
     </row>
     <row r="81" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -14689,6 +14770,7 @@
       <c r="DB84" s="25">
         <v>2026</v>
       </c>
+      <c r="DC84" s="25"/>
     </row>
     <row r="85" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -15008,6 +15090,9 @@
       </c>
       <c r="DB85" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC85" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15409,7 +15494,9 @@
       <c r="DB87" s="13">
         <v>123.61978579132276</v>
       </c>
-      <c r="DC87" s="20"/>
+      <c r="DC87" s="13">
+        <v>124.06261417077009</v>
+      </c>
       <c r="DD87" s="20"/>
       <c r="DE87" s="20"/>
       <c r="DF87" s="20"/>
@@ -15796,9 +15883,11 @@
         <v>130.03059961082388</v>
       </c>
       <c r="DB88" s="13">
-        <v>114.36304773982791</v>
-      </c>
-      <c r="DC88" s="20"/>
+        <v>114.36291191907473</v>
+      </c>
+      <c r="DC88" s="13">
+        <v>117.06977721898242</v>
+      </c>
       <c r="DD88" s="20"/>
       <c r="DE88" s="20"/>
       <c r="DF88" s="20"/>
@@ -15974,7 +16063,7 @@
       <c r="CZ89" s="8"/>
       <c r="DA89" s="8"/>
       <c r="DB89" s="8"/>
-      <c r="DC89" s="20"/>
+      <c r="DC89" s="8"/>
       <c r="DD89" s="20"/>
       <c r="DE89" s="20"/>
       <c r="DF89" s="20"/>
@@ -16361,9 +16450,11 @@
         <v>138.58236593565104</v>
       </c>
       <c r="DB90" s="13">
-        <v>120.56238349993838</v>
-      </c>
-      <c r="DC90" s="20"/>
+        <v>120.57604973903564</v>
+      </c>
+      <c r="DC90" s="13">
+        <v>122.12197297563765</v>
+      </c>
       <c r="DD90" s="20"/>
       <c r="DE90" s="20"/>
       <c r="DF90" s="20"/>
@@ -16540,6 +16631,7 @@
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
       <c r="DB91" s="10"/>
+      <c r="DC91" s="10"/>
     </row>
     <row r="92" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -16729,6 +16821,7 @@
       <c r="CZ93" s="4"/>
       <c r="DA93" s="4"/>
       <c r="DB93" s="4"/>
+      <c r="DC93" s="4"/>
     </row>
     <row r="94" spans="1:175" x14ac:dyDescent="0.25">
       <c r="B94" s="4"/>
@@ -16836,6 +16929,7 @@
       <c r="CZ94" s="4"/>
       <c r="DA94" s="4"/>
       <c r="DB94" s="4"/>
+      <c r="DC94" s="4"/>
     </row>
     <row r="95" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
@@ -16946,6 +17040,7 @@
       <c r="CZ95" s="4"/>
       <c r="DA95" s="4"/>
       <c r="DB95" s="4"/>
+      <c r="DC95" s="4"/>
     </row>
     <row r="96" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
@@ -17056,10 +17151,11 @@
       <c r="CZ96" s="4"/>
       <c r="DA96" s="4"/>
       <c r="DB96" s="4"/>
+      <c r="DC96" s="4"/>
     </row>
     <row r="97" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -17166,6 +17262,7 @@
       <c r="CZ97" s="4"/>
       <c r="DA97" s="4"/>
       <c r="DB97" s="4"/>
+      <c r="DC97" s="4"/>
     </row>
     <row r="98" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
@@ -17274,6 +17371,7 @@
       <c r="CZ98" s="4"/>
       <c r="DA98" s="4"/>
       <c r="DB98" s="4"/>
+      <c r="DC98" s="4"/>
     </row>
     <row r="99" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
@@ -17384,10 +17482,11 @@
       <c r="CZ99" s="4"/>
       <c r="DA99" s="4"/>
       <c r="DB99" s="4"/>
+      <c r="DC99" s="4"/>
     </row>
     <row r="100" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -17494,6 +17593,7 @@
       <c r="CZ100" s="4"/>
       <c r="DA100" s="4"/>
       <c r="DB100" s="4"/>
+      <c r="DC100" s="4"/>
     </row>
     <row r="101" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
@@ -17604,6 +17704,7 @@
       <c r="CZ101" s="4"/>
       <c r="DA101" s="4"/>
       <c r="DB101" s="4"/>
+      <c r="DC101" s="4"/>
     </row>
     <row r="102" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -17712,6 +17813,7 @@
       <c r="CZ102" s="4"/>
       <c r="DA102" s="4"/>
       <c r="DB102" s="4"/>
+      <c r="DC102" s="4"/>
     </row>
     <row r="103" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A103" s="14"/>
@@ -17874,6 +17976,7 @@
       <c r="DB103" s="25">
         <v>2026</v>
       </c>
+      <c r="DC103" s="25"/>
     </row>
     <row r="104" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -18193,6 +18296,9 @@
       </c>
       <c r="DB104" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC104" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -18302,6 +18408,7 @@
       <c r="CZ105" s="4"/>
       <c r="DA105" s="4"/>
       <c r="DB105" s="4"/>
+      <c r="DC105" s="4"/>
     </row>
     <row r="106" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
@@ -18620,9 +18727,11 @@
         <v>68.208981697067244</v>
       </c>
       <c r="DB106" s="13">
-        <v>68.669414723168316</v>
-      </c>
-      <c r="DC106" s="20"/>
+        <v>68.81348866304954</v>
+      </c>
+      <c r="DC106" s="13">
+        <v>73.396252093067829</v>
+      </c>
       <c r="DD106" s="20"/>
       <c r="DE106" s="20"/>
       <c r="DF106" s="20"/>
@@ -19013,9 +19122,11 @@
         <v>31.791018302932766</v>
       </c>
       <c r="DB107" s="13">
-        <v>31.33058527683168</v>
-      </c>
-      <c r="DC107" s="20"/>
+        <v>31.186511336950456</v>
+      </c>
+      <c r="DC107" s="13">
+        <v>26.603747906932163</v>
+      </c>
       <c r="DD107" s="20"/>
       <c r="DE107" s="20"/>
       <c r="DF107" s="20"/>
@@ -19195,7 +19306,7 @@
       <c r="CZ108" s="8"/>
       <c r="DA108" s="8"/>
       <c r="DB108" s="8"/>
-      <c r="DC108" s="20"/>
+      <c r="DC108" s="8"/>
       <c r="DD108" s="20"/>
       <c r="DE108" s="20"/>
       <c r="DF108" s="20"/>
@@ -19588,7 +19699,9 @@
       <c r="DB109" s="13">
         <v>100</v>
       </c>
-      <c r="DC109" s="20"/>
+      <c r="DC109" s="13">
+        <v>100</v>
+      </c>
       <c r="DD109" s="20"/>
       <c r="DE109" s="20"/>
       <c r="DF109" s="20"/>
@@ -19769,6 +19882,7 @@
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
       <c r="DB110" s="10"/>
+      <c r="DC110" s="10"/>
     </row>
     <row r="111" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -19879,6 +19993,7 @@
       <c r="CZ111" s="4"/>
       <c r="DA111" s="4"/>
       <c r="DB111" s="4"/>
+      <c r="DC111" s="4"/>
     </row>
     <row r="112" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="8"/>
@@ -19986,7 +20101,7 @@
       <c r="CZ112" s="8"/>
       <c r="DA112" s="8"/>
       <c r="DB112" s="8"/>
-      <c r="DC112" s="20"/>
+      <c r="DC112" s="8"/>
       <c r="DD112" s="20"/>
       <c r="DE112" s="20"/>
       <c r="DF112" s="20"/>
@@ -20166,7 +20281,7 @@
       <c r="CZ113" s="8"/>
       <c r="DA113" s="8"/>
       <c r="DB113" s="8"/>
-      <c r="DC113" s="20"/>
+      <c r="DC113" s="8"/>
       <c r="DD113" s="20"/>
       <c r="DE113" s="20"/>
       <c r="DF113" s="20"/>
@@ -20349,6 +20464,7 @@
       <c r="CZ114" s="4"/>
       <c r="DA114" s="4"/>
       <c r="DB114" s="4"/>
+      <c r="DC114" s="4"/>
     </row>
     <row r="115" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
@@ -20459,10 +20575,11 @@
       <c r="CZ115" s="4"/>
       <c r="DA115" s="4"/>
       <c r="DB115" s="4"/>
+      <c r="DC115" s="4"/>
     </row>
     <row r="116" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -20569,6 +20686,7 @@
       <c r="CZ116" s="4"/>
       <c r="DA116" s="4"/>
       <c r="DB116" s="4"/>
+      <c r="DC116" s="4"/>
     </row>
     <row r="117" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
@@ -20677,6 +20795,7 @@
       <c r="CZ117" s="4"/>
       <c r="DA117" s="4"/>
       <c r="DB117" s="4"/>
+      <c r="DC117" s="4"/>
     </row>
     <row r="118" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
@@ -20787,10 +20906,11 @@
       <c r="CZ118" s="4"/>
       <c r="DA118" s="4"/>
       <c r="DB118" s="4"/>
+      <c r="DC118" s="4"/>
     </row>
     <row r="119" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -20897,6 +21017,7 @@
       <c r="CZ119" s="4"/>
       <c r="DA119" s="4"/>
       <c r="DB119" s="4"/>
+      <c r="DC119" s="4"/>
     </row>
     <row r="120" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
@@ -21007,6 +21128,7 @@
       <c r="CZ120" s="4"/>
       <c r="DA120" s="4"/>
       <c r="DB120" s="4"/>
+      <c r="DC120" s="4"/>
     </row>
     <row r="121" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
@@ -21115,6 +21237,7 @@
       <c r="CZ121" s="4"/>
       <c r="DA121" s="4"/>
       <c r="DB121" s="4"/>
+      <c r="DC121" s="4"/>
     </row>
     <row r="122" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A122" s="14"/>
@@ -21277,6 +21400,7 @@
       <c r="DB122" s="25">
         <v>2026</v>
       </c>
+      <c r="DC122" s="25"/>
     </row>
     <row r="123" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -21596,6 +21720,9 @@
       </c>
       <c r="DB123" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC123" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -21705,6 +21832,7 @@
       <c r="CZ124" s="4"/>
       <c r="DA124" s="4"/>
       <c r="DB124" s="4"/>
+      <c r="DC124" s="4"/>
     </row>
     <row r="125" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
@@ -22023,9 +22151,11 @@
         <v>66.118171068117761</v>
       </c>
       <c r="DB125" s="13">
-        <v>66.971061788978275</v>
-      </c>
-      <c r="DC125" s="20"/>
+        <v>67.119179819310418</v>
+      </c>
+      <c r="DC125" s="13">
+        <v>72.248156098701045</v>
+      </c>
       <c r="DD125" s="20"/>
       <c r="DE125" s="20"/>
       <c r="DF125" s="20"/>
@@ -22416,9 +22546,11 @@
         <v>33.881828931882239</v>
       </c>
       <c r="DB126" s="13">
-        <v>33.028938211021732</v>
-      </c>
-      <c r="DC126" s="20"/>
+        <v>32.880820180689582</v>
+      </c>
+      <c r="DC126" s="13">
+        <v>27.751843901298969</v>
+      </c>
       <c r="DD126" s="20"/>
       <c r="DE126" s="20"/>
       <c r="DF126" s="20"/>
@@ -22598,7 +22730,7 @@
       <c r="CZ127" s="8"/>
       <c r="DA127" s="8"/>
       <c r="DB127" s="8"/>
-      <c r="DC127" s="20"/>
+      <c r="DC127" s="8"/>
       <c r="DD127" s="20"/>
       <c r="DE127" s="20"/>
       <c r="DF127" s="20"/>
@@ -22991,7 +23123,9 @@
       <c r="DB128" s="13">
         <v>100</v>
       </c>
-      <c r="DC128" s="20"/>
+      <c r="DC128" s="13">
+        <v>100</v>
+      </c>
       <c r="DD128" s="20"/>
       <c r="DE128" s="20"/>
       <c r="DF128" s="20"/>
@@ -23065,7 +23199,7 @@
       <c r="FV128" s="20"/>
       <c r="FW128" s="20"/>
     </row>
-    <row r="129" spans="1:106" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:107" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="10"/>
@@ -23172,8 +23306,9 @@
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
       <c r="DB129" s="10"/>
+      <c r="DC129" s="10"/>
     </row>
-    <row r="130" spans="1:106" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:107" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
         <v>6</v>
       </c>
@@ -23282,15 +23417,17 @@
       <c r="CZ130" s="4"/>
       <c r="DA130" s="4"/>
       <c r="DB130" s="4"/>
+      <c r="DC130" s="4"/>
     </row>
-    <row r="131" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CX131" s="23"/>
       <c r="CY131" s="23"/>
       <c r="CZ131" s="23"/>
       <c r="DA131" s="23"/>
       <c r="DB131" s="23"/>
+      <c r="DC131" s="23"/>
     </row>
-    <row r="132" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT132" s="24"/>
       <c r="CU132" s="24"/>
       <c r="CV132" s="24"/>
@@ -23299,8 +23436,9 @@
       <c r="CZ132" s="24"/>
       <c r="DA132" s="24"/>
       <c r="DB132" s="24"/>
+      <c r="DC132" s="24"/>
     </row>
-    <row r="133" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT133" s="24"/>
       <c r="CU133" s="24"/>
       <c r="CV133" s="24"/>
@@ -23309,8 +23447,9 @@
       <c r="CZ133" s="24"/>
       <c r="DA133" s="24"/>
       <c r="DB133" s="24"/>
+      <c r="DC133" s="24"/>
     </row>
-    <row r="134" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT134" s="24"/>
       <c r="CU134" s="24"/>
       <c r="CV134" s="24"/>
@@ -23319,8 +23458,9 @@
       <c r="CZ134" s="24"/>
       <c r="DA134" s="24"/>
       <c r="DB134" s="24"/>
+      <c r="DC134" s="24"/>
     </row>
-    <row r="135" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT135" s="24"/>
       <c r="CU135" s="24"/>
       <c r="CV135" s="24"/>
@@ -23329,8 +23469,9 @@
       <c r="CZ135" s="24"/>
       <c r="DA135" s="24"/>
       <c r="DB135" s="24"/>
+      <c r="DC135" s="24"/>
     </row>
-    <row r="136" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT136" s="24"/>
       <c r="CU136" s="24"/>
       <c r="CV136" s="24"/>
@@ -23339,8 +23480,9 @@
       <c r="CZ136" s="24"/>
       <c r="DA136" s="24"/>
       <c r="DB136" s="24"/>
+      <c r="DC136" s="24"/>
     </row>
-    <row r="137" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT137" s="24"/>
       <c r="CU137" s="24"/>
       <c r="CV137" s="24"/>
@@ -23349,8 +23491,9 @@
       <c r="CZ137" s="24"/>
       <c r="DA137" s="24"/>
       <c r="DB137" s="24"/>
+      <c r="DC137" s="24"/>
     </row>
-    <row r="138" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT138" s="24"/>
       <c r="CU138" s="24"/>
       <c r="CV138" s="24"/>
@@ -23359,8 +23502,9 @@
       <c r="CZ138" s="24"/>
       <c r="DA138" s="24"/>
       <c r="DB138" s="24"/>
+      <c r="DC138" s="24"/>
     </row>
-    <row r="139" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT139" s="24"/>
       <c r="CU139" s="24"/>
       <c r="CV139" s="24"/>
@@ -23369,8 +23513,9 @@
       <c r="CZ139" s="24"/>
       <c r="DA139" s="24"/>
       <c r="DB139" s="24"/>
+      <c r="DC139" s="24"/>
     </row>
-    <row r="140" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT140" s="24"/>
       <c r="CU140" s="24"/>
       <c r="CV140" s="24"/>
@@ -23379,8 +23524,9 @@
       <c r="CZ140" s="24"/>
       <c r="DA140" s="24"/>
       <c r="DB140" s="24"/>
+      <c r="DC140" s="24"/>
     </row>
-    <row r="141" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT141" s="24"/>
       <c r="CU141" s="24"/>
       <c r="CV141" s="24"/>
@@ -23389,8 +23535,9 @@
       <c r="CZ141" s="24"/>
       <c r="DA141" s="24"/>
       <c r="DB141" s="24"/>
+      <c r="DC141" s="24"/>
     </row>
-    <row r="142" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT142" s="24"/>
       <c r="CU142" s="24"/>
       <c r="CV142" s="24"/>
@@ -23399,8 +23546,9 @@
       <c r="CZ142" s="24"/>
       <c r="DA142" s="24"/>
       <c r="DB142" s="24"/>
+      <c r="DC142" s="24"/>
     </row>
-    <row r="143" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT143" s="24"/>
       <c r="CU143" s="24"/>
       <c r="CV143" s="24"/>
@@ -23409,8 +23557,9 @@
       <c r="CZ143" s="24"/>
       <c r="DA143" s="24"/>
       <c r="DB143" s="24"/>
+      <c r="DC143" s="24"/>
     </row>
-    <row r="144" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT144" s="24"/>
       <c r="CU144" s="24"/>
       <c r="CV144" s="24"/>
@@ -23419,8 +23568,9 @@
       <c r="CZ144" s="24"/>
       <c r="DA144" s="24"/>
       <c r="DB144" s="24"/>
+      <c r="DC144" s="24"/>
     </row>
-    <row r="145" spans="98:106" x14ac:dyDescent="0.25">
+    <row r="145" spans="98:107" x14ac:dyDescent="0.25">
       <c r="CT145" s="24"/>
       <c r="CU145" s="24"/>
       <c r="CV145" s="24"/>
@@ -23429,8 +23579,9 @@
       <c r="CZ145" s="24"/>
       <c r="DA145" s="24"/>
       <c r="DB145" s="24"/>
+      <c r="DC145" s="24"/>
     </row>
-    <row r="146" spans="98:106" x14ac:dyDescent="0.25">
+    <row r="146" spans="98:107" x14ac:dyDescent="0.25">
       <c r="CT146" s="24"/>
       <c r="CU146" s="24"/>
       <c r="CV146" s="24"/>
@@ -23439,8 +23590,9 @@
       <c r="CZ146" s="24"/>
       <c r="DA146" s="24"/>
       <c r="DB146" s="24"/>
+      <c r="DC146" s="24"/>
     </row>
-    <row r="147" spans="98:106" x14ac:dyDescent="0.25">
+    <row r="147" spans="98:107" x14ac:dyDescent="0.25">
       <c r="CT147" s="24"/>
       <c r="CU147" s="24"/>
       <c r="CV147" s="24"/>
@@ -23449,15 +23601,12 @@
       <c r="CZ147" s="24"/>
       <c r="DA147" s="24"/>
       <c r="DB147" s="24"/>
+      <c r="DC147" s="24"/>
     </row>
-    <row r="148" spans="98:106" x14ac:dyDescent="0.25">
+    <row r="148" spans="98:107" x14ac:dyDescent="0.25">
       <c r="CT148" s="24"/>
       <c r="CU148" s="24"/>
       <c r="CV148" s="24"/>
-      <c r="CX148" s="24"/>
-      <c r="CY148" s="24"/>
-      <c r="CZ148" s="24"/>
-      <c r="DA148" s="24"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -23465,9 +23614,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="105" man="1"/>
-    <brk id="76" max="105" man="1"/>
-    <brk id="94" max="105" man="1"/>
+    <brk id="38" max="106" man="1"/>
+    <brk id="76" max="106" man="1"/>
+    <brk id="94" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>